--- a/web/public/2027학년도_수시_교대경쟁률취합_정보분석3팀_최신.xlsx
+++ b/web/public/2027학년도_수시_교대경쟁률취합_정보분석3팀_최신.xlsx
@@ -506,13 +506,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q15"/>
+  <dimension ref="A1:S15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="39" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -526,6 +526,8 @@
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -576,11 +578,17 @@
         </is>
       </c>
       <c r="Q1" s="2" t="n"/>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>최종</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="D2" t="inlineStr">
         <is>
-          <t>대학의 마감일에는 10시, 14시, 15시, 최종해주시면 됩니다.</t>
+          <t>2027 수시모집 최종 경쟁률 마감 현황</t>
         </is>
       </c>
     </row>
@@ -672,6 +680,16 @@
           <t>경쟁률</t>
         </is>
       </c>
+      <c r="Q4" s="4" t="inlineStr">
+        <is>
+          <t>지원인원</t>
+        </is>
+      </c>
+      <c r="R4" s="4" t="inlineStr">
+        <is>
+          <t>경쟁률</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -754,6 +772,16 @@
           <t>6.74 : 1</t>
         </is>
       </c>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>2,819</t>
+        </is>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>7.01 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -843,6 +871,16 @@
           <t>경쟁률</t>
         </is>
       </c>
+      <c r="Q7" s="4" t="inlineStr">
+        <is>
+          <t>지원인원</t>
+        </is>
+      </c>
+      <c r="R7" s="4" t="inlineStr">
+        <is>
+          <t>경쟁률</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -925,6 +963,16 @@
           <t>4.95 : 1</t>
         </is>
       </c>
+      <c r="Q8" s="8" t="inlineStr">
+        <is>
+          <t>574</t>
+        </is>
+      </c>
+      <c r="R8" s="8" t="inlineStr">
+        <is>
+          <t>5.22 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -1007,6 +1055,16 @@
           <t>8.03 : 1</t>
         </is>
       </c>
+      <c r="Q9" s="8" t="inlineStr">
+        <is>
+          <t>1,887</t>
+        </is>
+      </c>
+      <c r="R9" s="8" t="inlineStr">
+        <is>
+          <t>8.35 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -1089,6 +1147,16 @@
           <t>5.50 : 1</t>
         </is>
       </c>
+      <c r="Q10" s="8" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="R10" s="8" t="inlineStr">
+        <is>
+          <t>5.50 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -1171,6 +1239,16 @@
           <t>6.94 : 1</t>
         </is>
       </c>
+      <c r="Q11" s="8" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="R11" s="8" t="inlineStr">
+        <is>
+          <t>7.11 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -1253,6 +1331,16 @@
           <t>5.10 : 1</t>
         </is>
       </c>
+      <c r="Q12" s="8" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="R12" s="8" t="inlineStr">
+        <is>
+          <t>5.14 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -1335,6 +1423,16 @@
           <t>4.75 : 1</t>
         </is>
       </c>
+      <c r="Q13" s="8" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="R13" s="8" t="inlineStr">
+        <is>
+          <t>4.85 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -1417,6 +1515,16 @@
           <t>1.00 : 1</t>
         </is>
       </c>
+      <c r="Q14" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R14" s="8" t="inlineStr">
+        <is>
+          <t>1.00 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -1499,9 +1607,19 @@
           <t>6.74 : 1</t>
         </is>
       </c>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>2,819</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>7.01 : 1</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="N1:O1"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="D1:E1"/>
@@ -1510,6 +1628,7 @@
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="F1:G1"/>
+    <mergeCell ref="R1:S1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1521,13 +1640,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:S12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="39" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -1541,6 +1660,8 @@
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1591,11 +1712,17 @@
         </is>
       </c>
       <c r="Q1" s="2" t="n"/>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>최종</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="D2" t="inlineStr">
         <is>
-          <t>대학의 마감일에는 10시, 14시, 15시, 최종해주시면 됩니다.</t>
+          <t>2027 수시모집 최종 경쟁률 마감 현황</t>
         </is>
       </c>
     </row>
@@ -1687,6 +1814,16 @@
           <t>경쟁률</t>
         </is>
       </c>
+      <c r="Q4" s="4" t="inlineStr">
+        <is>
+          <t>지원인원</t>
+        </is>
+      </c>
+      <c r="R4" s="4" t="inlineStr">
+        <is>
+          <t>경쟁률</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
@@ -1769,6 +1906,16 @@
           <t>13.81 : 1</t>
         </is>
       </c>
+      <c r="Q5" s="8" t="inlineStr">
+        <is>
+          <t>1,401</t>
+        </is>
+      </c>
+      <c r="R5" s="8" t="inlineStr">
+        <is>
+          <t>14.59 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -1851,6 +1998,16 @@
           <t>4.43 : 1</t>
         </is>
       </c>
+      <c r="Q6" s="8" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="R6" s="8" t="inlineStr">
+        <is>
+          <t>4.67 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -1933,6 +2090,16 @@
           <t>9.50 : 1</t>
         </is>
       </c>
+      <c r="Q7" s="8" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="R7" s="8" t="inlineStr">
+        <is>
+          <t>10.00 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -2015,6 +2182,16 @@
           <t>8.50 : 1</t>
         </is>
       </c>
+      <c r="Q8" s="8" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R8" s="8" t="inlineStr">
+        <is>
+          <t>8.50 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -2097,6 +2274,16 @@
           <t>9.00 : 1</t>
         </is>
       </c>
+      <c r="Q9" s="8" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="R9" s="8" t="inlineStr">
+        <is>
+          <t>9.50 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -2179,6 +2366,16 @@
           <t>11.60 : 1</t>
         </is>
       </c>
+      <c r="Q10" s="8" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="R10" s="8" t="inlineStr">
+        <is>
+          <t>12.40 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -2261,6 +2458,16 @@
           <t>5.40 : 1</t>
         </is>
       </c>
+      <c r="Q11" s="8" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="R11" s="8" t="inlineStr">
+        <is>
+          <t>5.40 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -2343,9 +2550,19 @@
           <t>10.00 : 1</t>
         </is>
       </c>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>1,941</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>10.55 : 1</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="N1:O1"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="D1:E1"/>
@@ -2354,6 +2571,7 @@
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="F1:G1"/>
+    <mergeCell ref="R1:S1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2365,13 +2583,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="39" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -2385,6 +2603,8 @@
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2435,11 +2655,17 @@
         </is>
       </c>
       <c r="Q1" s="2" t="n"/>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>최종</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="D2" t="inlineStr">
         <is>
-          <t>대학의 마감일에는 10시, 14시, 15시, 최종해주시면 됩니다.</t>
+          <t>2027 수시모집 최종 경쟁률 마감 현황</t>
         </is>
       </c>
     </row>
@@ -2527,6 +2753,16 @@
         </is>
       </c>
       <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t>경쟁률</t>
+        </is>
+      </c>
+      <c r="Q4" s="4" t="inlineStr">
+        <is>
+          <t>지원인원</t>
+        </is>
+      </c>
+      <c r="R4" s="4" t="inlineStr">
         <is>
           <t>경쟁률</t>
         </is>
@@ -2589,6 +2825,8 @@
       <c r="N5" s="8" t="inlineStr"/>
       <c r="O5" s="8" t="inlineStr"/>
       <c r="P5" s="8" t="inlineStr"/>
+      <c r="Q5" s="8" t="inlineStr"/>
+      <c r="R5" s="8" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -2647,6 +2885,8 @@
       <c r="N6" s="8" t="inlineStr"/>
       <c r="O6" s="8" t="inlineStr"/>
       <c r="P6" s="8" t="inlineStr"/>
+      <c r="Q6" s="8" t="inlineStr"/>
+      <c r="R6" s="8" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -2705,9 +2945,11 @@
       <c r="N7" s="6" t="inlineStr"/>
       <c r="O7" s="6" t="inlineStr"/>
       <c r="P7" s="6" t="inlineStr"/>
+      <c r="Q7" s="6" t="inlineStr"/>
+      <c r="R7" s="6" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="N1:O1"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="D1:E1"/>
@@ -2716,6 +2958,7 @@
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="F1:G1"/>
+    <mergeCell ref="R1:S1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2727,13 +2970,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="39" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -2747,6 +2990,8 @@
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2797,11 +3042,17 @@
         </is>
       </c>
       <c r="Q1" s="2" t="n"/>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>최종</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="D2" t="inlineStr">
         <is>
-          <t>대학의 마감일에는 10시, 14시, 15시, 최종해주시면 됩니다.</t>
+          <t>2027 수시모집 최종 경쟁률 마감 현황</t>
         </is>
       </c>
     </row>
@@ -2900,6 +3151,16 @@
           <t>경쟁률</t>
         </is>
       </c>
+      <c r="Q5" s="4" t="inlineStr">
+        <is>
+          <t>지원인원</t>
+        </is>
+      </c>
+      <c r="R5" s="4" t="inlineStr">
+        <is>
+          <t>경쟁률</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -2982,9 +3243,19 @@
           <t>28.60 : 1</t>
         </is>
       </c>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>9,208</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>28.60 : 1</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="N1:O1"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="D1:E1"/>
@@ -2993,6 +3264,7 @@
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="F1:G1"/>
+    <mergeCell ref="R1:S1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3004,13 +3276,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q29"/>
+  <dimension ref="A1:S29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="39" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -3024,6 +3296,8 @@
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3074,11 +3348,17 @@
         </is>
       </c>
       <c r="Q1" s="2" t="n"/>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>최종</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="D2" t="inlineStr">
         <is>
-          <t>대학의 마감일에는 10시, 14시, 15시, 최종해주시면 됩니다.</t>
+          <t>2027 수시모집 최종 경쟁률 마감 현황</t>
         </is>
       </c>
     </row>
@@ -3170,6 +3450,16 @@
           <t>경쟁률</t>
         </is>
       </c>
+      <c r="Q4" s="4" t="inlineStr">
+        <is>
+          <t>지원인원</t>
+        </is>
+      </c>
+      <c r="R4" s="4" t="inlineStr">
+        <is>
+          <t>경쟁률</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -3252,6 +3542,16 @@
           <t>13.02 : 1</t>
         </is>
       </c>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>4,536</t>
+        </is>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>14.40 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -3341,6 +3641,16 @@
           <t>경쟁률</t>
         </is>
       </c>
+      <c r="Q7" s="4" t="inlineStr">
+        <is>
+          <t>지원인원</t>
+        </is>
+      </c>
+      <c r="R7" s="4" t="inlineStr">
+        <is>
+          <t>경쟁률</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -3423,6 +3733,16 @@
           <t>12.47 : 1</t>
         </is>
       </c>
+      <c r="Q8" s="8" t="inlineStr">
+        <is>
+          <t>2,979</t>
+        </is>
+      </c>
+      <c r="R8" s="8" t="inlineStr">
+        <is>
+          <t>13.54 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -3505,6 +3825,16 @@
           <t>12.63 : 1</t>
         </is>
       </c>
+      <c r="Q9" s="8" t="inlineStr">
+        <is>
+          <t>876</t>
+        </is>
+      </c>
+      <c r="R9" s="8" t="inlineStr">
+        <is>
+          <t>14.60 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -3587,6 +3917,16 @@
           <t>15.96 : 1</t>
         </is>
       </c>
+      <c r="Q10" s="8" t="inlineStr">
+        <is>
+          <t>447</t>
+        </is>
+      </c>
+      <c r="R10" s="8" t="inlineStr">
+        <is>
+          <t>17.88 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -3669,6 +4009,16 @@
           <t>20.00 : 1</t>
         </is>
       </c>
+      <c r="Q11" s="8" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="R11" s="8" t="inlineStr">
+        <is>
+          <t>23.40 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -3751,6 +4101,16 @@
           <t>13.02 : 1</t>
         </is>
       </c>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>4,536</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>14.40 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -3840,6 +4200,16 @@
           <t>경쟁률</t>
         </is>
       </c>
+      <c r="Q14" s="4" t="inlineStr">
+        <is>
+          <t>지원인원</t>
+        </is>
+      </c>
+      <c r="R14" s="4" t="inlineStr">
+        <is>
+          <t>경쟁률</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
@@ -3922,6 +4292,16 @@
           <t>12.66 : 1</t>
         </is>
       </c>
+      <c r="Q15" s="8" t="inlineStr">
+        <is>
+          <t>2,690</t>
+        </is>
+      </c>
+      <c r="R15" s="8" t="inlineStr">
+        <is>
+          <t>13.79 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
@@ -4004,6 +4384,16 @@
           <t>11.00 : 1</t>
         </is>
       </c>
+      <c r="Q16" s="8" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="R16" s="8" t="inlineStr">
+        <is>
+          <t>11.56 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
@@ -4086,6 +4476,16 @@
           <t>12.47 : 1</t>
         </is>
       </c>
+      <c r="Q17" s="8" t="inlineStr">
+        <is>
+          <t>2,979</t>
+        </is>
+      </c>
+      <c r="R17" s="8" t="inlineStr">
+        <is>
+          <t>13.54 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -4175,6 +4575,16 @@
           <t>경쟁률</t>
         </is>
       </c>
+      <c r="Q19" s="4" t="inlineStr">
+        <is>
+          <t>지원인원</t>
+        </is>
+      </c>
+      <c r="R19" s="4" t="inlineStr">
+        <is>
+          <t>경쟁률</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
@@ -4257,6 +4667,16 @@
           <t>12.63 : 1</t>
         </is>
       </c>
+      <c r="Q20" s="8" t="inlineStr">
+        <is>
+          <t>876</t>
+        </is>
+      </c>
+      <c r="R20" s="8" t="inlineStr">
+        <is>
+          <t>14.60 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
@@ -4339,6 +4759,16 @@
           <t>12.63 : 1</t>
         </is>
       </c>
+      <c r="Q21" s="8" t="inlineStr">
+        <is>
+          <t>876</t>
+        </is>
+      </c>
+      <c r="R21" s="8" t="inlineStr">
+        <is>
+          <t>14.60 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
@@ -4428,6 +4858,16 @@
           <t>경쟁률</t>
         </is>
       </c>
+      <c r="Q23" s="4" t="inlineStr">
+        <is>
+          <t>지원인원</t>
+        </is>
+      </c>
+      <c r="R23" s="4" t="inlineStr">
+        <is>
+          <t>경쟁률</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
@@ -4510,6 +4950,16 @@
           <t>15.96 : 1</t>
         </is>
       </c>
+      <c r="Q24" s="8" t="inlineStr">
+        <is>
+          <t>447</t>
+        </is>
+      </c>
+      <c r="R24" s="8" t="inlineStr">
+        <is>
+          <t>17.88 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
@@ -4592,6 +5042,16 @@
           <t>15.96 : 1</t>
         </is>
       </c>
+      <c r="Q25" s="8" t="inlineStr">
+        <is>
+          <t>447</t>
+        </is>
+      </c>
+      <c r="R25" s="8" t="inlineStr">
+        <is>
+          <t>17.88 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -4681,6 +5141,16 @@
           <t>경쟁률</t>
         </is>
       </c>
+      <c r="Q27" s="4" t="inlineStr">
+        <is>
+          <t>지원인원</t>
+        </is>
+      </c>
+      <c r="R27" s="4" t="inlineStr">
+        <is>
+          <t>경쟁률</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
@@ -4763,6 +5233,16 @@
           <t>20.00 : 1</t>
         </is>
       </c>
+      <c r="Q28" s="8" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="R28" s="8" t="inlineStr">
+        <is>
+          <t>23.40 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
@@ -4845,9 +5325,19 @@
           <t>20.00 : 1</t>
         </is>
       </c>
+      <c r="Q29" s="8" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="R29" s="8" t="inlineStr">
+        <is>
+          <t>23.40 : 1</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="N1:O1"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="D1:E1"/>
@@ -4856,6 +5346,7 @@
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="F1:G1"/>
+    <mergeCell ref="R1:S1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4867,13 +5358,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:S14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="39" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -4887,6 +5378,8 @@
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4937,11 +5430,17 @@
         </is>
       </c>
       <c r="Q1" s="2" t="n"/>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>최종</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="D2" t="inlineStr">
         <is>
-          <t>대학의 마감일에는 10시, 14시, 15시, 최종해주시면 됩니다.</t>
+          <t>2027 수시모집 최종 경쟁률 마감 현황</t>
         </is>
       </c>
     </row>
@@ -5033,6 +5532,16 @@
           <t>경쟁률</t>
         </is>
       </c>
+      <c r="Q4" s="4" t="inlineStr">
+        <is>
+          <t>지원인원</t>
+        </is>
+      </c>
+      <c r="R4" s="4" t="inlineStr">
+        <is>
+          <t>경쟁률</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -5115,6 +5624,16 @@
           <t>9.70 : 1</t>
         </is>
       </c>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>8,394</t>
+        </is>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>9.70 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -5204,6 +5723,16 @@
           <t>경쟁률</t>
         </is>
       </c>
+      <c r="Q7" s="4" t="inlineStr">
+        <is>
+          <t>지원인원</t>
+        </is>
+      </c>
+      <c r="R7" s="4" t="inlineStr">
+        <is>
+          <t>경쟁률</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -5286,6 +5815,16 @@
           <t>10.09 : 1</t>
         </is>
       </c>
+      <c r="Q8" s="8" t="inlineStr">
+        <is>
+          <t>2,724</t>
+        </is>
+      </c>
+      <c r="R8" s="8" t="inlineStr">
+        <is>
+          <t>10.09 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -5368,6 +5907,16 @@
           <t>17.81 : 1</t>
         </is>
       </c>
+      <c r="Q9" s="8" t="inlineStr">
+        <is>
+          <t>1,514</t>
+        </is>
+      </c>
+      <c r="R9" s="8" t="inlineStr">
+        <is>
+          <t>17.81 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -5450,6 +5999,16 @@
           <t>8.43 : 1</t>
         </is>
       </c>
+      <c r="Q10" s="8" t="inlineStr">
+        <is>
+          <t>3,204</t>
+        </is>
+      </c>
+      <c r="R10" s="8" t="inlineStr">
+        <is>
+          <t>8.43 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -5532,6 +6091,16 @@
           <t>8.00 : 1</t>
         </is>
       </c>
+      <c r="Q11" s="8" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="R11" s="8" t="inlineStr">
+        <is>
+          <t>8.00 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -5614,6 +6183,16 @@
           <t>9.57 : 1</t>
         </is>
       </c>
+      <c r="Q12" s="8" t="inlineStr">
+        <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="R12" s="8" t="inlineStr">
+        <is>
+          <t>9.57 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -5696,6 +6275,16 @@
           <t>4.63 : 1</t>
         </is>
       </c>
+      <c r="Q13" s="8" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="R13" s="8" t="inlineStr">
+        <is>
+          <t>4.63 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -5778,9 +6367,19 @@
           <t>9.70 : 1</t>
         </is>
       </c>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>8,394</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>9.70 : 1</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="N1:O1"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="D1:E1"/>
@@ -5789,6 +6388,7 @@
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="F1:G1"/>
+    <mergeCell ref="R1:S1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5800,13 +6400,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q10"/>
+  <dimension ref="A1:S10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="39" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -5820,6 +6420,8 @@
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5870,11 +6472,17 @@
         </is>
       </c>
       <c r="Q1" s="2" t="n"/>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>최종</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="D2" t="inlineStr">
         <is>
-          <t>대학의 마감일에는 10시, 14시, 15시, 최종해주시면 됩니다.</t>
+          <t>2027 수시모집 최종 경쟁률 마감 현황</t>
         </is>
       </c>
     </row>
@@ -5966,6 +6574,16 @@
           <t>경쟁률</t>
         </is>
       </c>
+      <c r="Q4" s="4" t="inlineStr">
+        <is>
+          <t>지원인원</t>
+        </is>
+      </c>
+      <c r="R4" s="4" t="inlineStr">
+        <is>
+          <t>경쟁률</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -6048,6 +6666,16 @@
           <t>29.62 : 1</t>
         </is>
       </c>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>2,962</t>
+        </is>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>29.62 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -6137,6 +6765,16 @@
           <t>경쟁률</t>
         </is>
       </c>
+      <c r="Q7" s="4" t="inlineStr">
+        <is>
+          <t>지원인원</t>
+        </is>
+      </c>
+      <c r="R7" s="4" t="inlineStr">
+        <is>
+          <t>경쟁률</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -6219,6 +6857,16 @@
           <t>30.11 : 1</t>
         </is>
       </c>
+      <c r="Q8" s="8" t="inlineStr">
+        <is>
+          <t>2,710</t>
+        </is>
+      </c>
+      <c r="R8" s="8" t="inlineStr">
+        <is>
+          <t>30.11 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -6301,6 +6949,16 @@
           <t>25.20 : 1</t>
         </is>
       </c>
+      <c r="Q9" s="8" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="R9" s="8" t="inlineStr">
+        <is>
+          <t>25.20 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -6383,9 +7041,19 @@
           <t>29.62 : 1</t>
         </is>
       </c>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>2,962</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>29.62 : 1</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="N1:O1"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="D1:E1"/>
@@ -6394,6 +7062,7 @@
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="F1:G1"/>
+    <mergeCell ref="R1:S1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6405,13 +7074,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q38"/>
+  <dimension ref="A1:S38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="39" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -6425,6 +7094,8 @@
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6475,11 +7146,17 @@
         </is>
       </c>
       <c r="Q1" s="2" t="n"/>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>최종</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="D2" t="inlineStr">
         <is>
-          <t>대학의 마감일에는 10시, 14시, 15시, 최종해주시면 됩니다.</t>
+          <t>2027 수시모집 최종 경쟁률 마감 현황</t>
         </is>
       </c>
     </row>
@@ -6571,6 +7248,16 @@
           <t>경쟁률</t>
         </is>
       </c>
+      <c r="Q4" s="4" t="inlineStr">
+        <is>
+          <t>지원인원</t>
+        </is>
+      </c>
+      <c r="R4" s="4" t="inlineStr">
+        <is>
+          <t>경쟁률</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -6653,6 +7340,16 @@
           <t>9.33 : 1</t>
         </is>
       </c>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>3,453</t>
+        </is>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>9.33 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -6742,6 +7439,16 @@
           <t>경쟁률</t>
         </is>
       </c>
+      <c r="Q7" s="4" t="inlineStr">
+        <is>
+          <t>지원인원</t>
+        </is>
+      </c>
+      <c r="R7" s="4" t="inlineStr">
+        <is>
+          <t>경쟁률</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -6824,6 +7531,16 @@
           <t>8.64 : 1</t>
         </is>
       </c>
+      <c r="Q8" s="8" t="inlineStr">
+        <is>
+          <t>1,901</t>
+        </is>
+      </c>
+      <c r="R8" s="8" t="inlineStr">
+        <is>
+          <t>8.64 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -6906,6 +7623,16 @@
           <t>11.27 : 1</t>
         </is>
       </c>
+      <c r="Q9" s="8" t="inlineStr">
+        <is>
+          <t>789</t>
+        </is>
+      </c>
+      <c r="R9" s="8" t="inlineStr">
+        <is>
+          <t>11.27 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -6988,6 +7715,16 @@
           <t>6.30 : 1</t>
         </is>
       </c>
+      <c r="Q10" s="8" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="R10" s="8" t="inlineStr">
+        <is>
+          <t>6.30 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -7070,6 +7807,16 @@
           <t>12.70 : 1</t>
         </is>
       </c>
+      <c r="Q11" s="8" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="R11" s="8" t="inlineStr">
+        <is>
+          <t>12.70 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -7152,6 +7899,16 @@
           <t>6.80 : 1</t>
         </is>
       </c>
+      <c r="Q12" s="8" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="R12" s="8" t="inlineStr">
+        <is>
+          <t>6.80 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -7234,6 +7991,16 @@
           <t>11.05 : 1</t>
         </is>
       </c>
+      <c r="Q13" s="8" t="inlineStr">
+        <is>
+          <t>442</t>
+        </is>
+      </c>
+      <c r="R13" s="8" t="inlineStr">
+        <is>
+          <t>11.05 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -7316,6 +8083,16 @@
           <t>9.33 : 1</t>
         </is>
       </c>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>3,453</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>9.33 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -7405,6 +8182,16 @@
           <t>경쟁률</t>
         </is>
       </c>
+      <c r="Q16" s="4" t="inlineStr">
+        <is>
+          <t>지원인원</t>
+        </is>
+      </c>
+      <c r="R16" s="4" t="inlineStr">
+        <is>
+          <t>경쟁률</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
@@ -7487,6 +8274,16 @@
           <t>8.64 : 1</t>
         </is>
       </c>
+      <c r="Q17" s="8" t="inlineStr">
+        <is>
+          <t>1,901</t>
+        </is>
+      </c>
+      <c r="R17" s="8" t="inlineStr">
+        <is>
+          <t>8.64 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
@@ -7569,6 +8366,16 @@
           <t>8.64 : 1</t>
         </is>
       </c>
+      <c r="Q18" s="8" t="inlineStr">
+        <is>
+          <t>1,901</t>
+        </is>
+      </c>
+      <c r="R18" s="8" t="inlineStr">
+        <is>
+          <t>8.64 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -7658,6 +8465,16 @@
           <t>경쟁률</t>
         </is>
       </c>
+      <c r="Q20" s="4" t="inlineStr">
+        <is>
+          <t>지원인원</t>
+        </is>
+      </c>
+      <c r="R20" s="4" t="inlineStr">
+        <is>
+          <t>경쟁률</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
@@ -7740,6 +8557,16 @@
           <t>11.27 : 1</t>
         </is>
       </c>
+      <c r="Q21" s="8" t="inlineStr">
+        <is>
+          <t>789</t>
+        </is>
+      </c>
+      <c r="R21" s="8" t="inlineStr">
+        <is>
+          <t>11.27 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
@@ -7822,6 +8649,16 @@
           <t>11.27 : 1</t>
         </is>
       </c>
+      <c r="Q22" s="8" t="inlineStr">
+        <is>
+          <t>789</t>
+        </is>
+      </c>
+      <c r="R22" s="8" t="inlineStr">
+        <is>
+          <t>11.27 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -7911,6 +8748,16 @@
           <t>경쟁률</t>
         </is>
       </c>
+      <c r="Q24" s="4" t="inlineStr">
+        <is>
+          <t>지원인원</t>
+        </is>
+      </c>
+      <c r="R24" s="4" t="inlineStr">
+        <is>
+          <t>경쟁률</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
@@ -7993,6 +8840,16 @@
           <t>6.30 : 1</t>
         </is>
       </c>
+      <c r="Q25" s="8" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="R25" s="8" t="inlineStr">
+        <is>
+          <t>6.30 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
@@ -8075,6 +8932,16 @@
           <t>6.30 : 1</t>
         </is>
       </c>
+      <c r="Q26" s="8" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="R26" s="8" t="inlineStr">
+        <is>
+          <t>6.30 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -8164,6 +9031,16 @@
           <t>경쟁률</t>
         </is>
       </c>
+      <c r="Q28" s="4" t="inlineStr">
+        <is>
+          <t>지원인원</t>
+        </is>
+      </c>
+      <c r="R28" s="4" t="inlineStr">
+        <is>
+          <t>경쟁률</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
@@ -8246,6 +9123,16 @@
           <t>12.70 : 1</t>
         </is>
       </c>
+      <c r="Q29" s="8" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="R29" s="8" t="inlineStr">
+        <is>
+          <t>12.70 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
@@ -8328,6 +9215,16 @@
           <t>12.70 : 1</t>
         </is>
       </c>
+      <c r="Q30" s="8" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="R30" s="8" t="inlineStr">
+        <is>
+          <t>12.70 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -8417,6 +9314,16 @@
           <t>경쟁률</t>
         </is>
       </c>
+      <c r="Q32" s="4" t="inlineStr">
+        <is>
+          <t>지원인원</t>
+        </is>
+      </c>
+      <c r="R32" s="4" t="inlineStr">
+        <is>
+          <t>경쟁률</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
@@ -8499,6 +9406,16 @@
           <t>6.80 : 1</t>
         </is>
       </c>
+      <c r="Q33" s="8" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="R33" s="8" t="inlineStr">
+        <is>
+          <t>6.80 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
@@ -8581,6 +9498,16 @@
           <t>6.80 : 1</t>
         </is>
       </c>
+      <c r="Q34" s="8" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="R34" s="8" t="inlineStr">
+        <is>
+          <t>6.80 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
@@ -8670,6 +9597,16 @@
           <t>경쟁률</t>
         </is>
       </c>
+      <c r="Q36" s="4" t="inlineStr">
+        <is>
+          <t>지원인원</t>
+        </is>
+      </c>
+      <c r="R36" s="4" t="inlineStr">
+        <is>
+          <t>경쟁률</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
@@ -8752,6 +9689,16 @@
           <t>11.05 : 1</t>
         </is>
       </c>
+      <c r="Q37" s="8" t="inlineStr">
+        <is>
+          <t>442</t>
+        </is>
+      </c>
+      <c r="R37" s="8" t="inlineStr">
+        <is>
+          <t>11.05 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
@@ -8834,9 +9781,19 @@
           <t>11.05 : 1</t>
         </is>
       </c>
+      <c r="Q38" s="8" t="inlineStr">
+        <is>
+          <t>442</t>
+        </is>
+      </c>
+      <c r="R38" s="8" t="inlineStr">
+        <is>
+          <t>11.05 : 1</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="N1:O1"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="D1:E1"/>
@@ -8845,6 +9802,7 @@
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="F1:G1"/>
+    <mergeCell ref="R1:S1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8856,13 +9814,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="39" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -8876,6 +9834,8 @@
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8926,11 +9886,17 @@
         </is>
       </c>
       <c r="Q1" s="2" t="n"/>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>최종</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="D2" t="inlineStr">
         <is>
-          <t>대학의 마감일에는 10시, 14시, 15시, 최종해주시면 됩니다.</t>
+          <t>2027 수시모집 최종 경쟁률 마감 현황</t>
         </is>
       </c>
     </row>
@@ -9029,6 +9995,16 @@
           <t>경쟁률</t>
         </is>
       </c>
+      <c r="Q5" s="4" t="inlineStr">
+        <is>
+          <t>지원인원</t>
+        </is>
+      </c>
+      <c r="R5" s="4" t="inlineStr">
+        <is>
+          <t>경쟁률</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -9111,9 +10087,19 @@
           <t>19.84 : 1</t>
         </is>
       </c>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>11,211</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>19.84 : 1</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="N1:O1"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="D1:E1"/>
@@ -9122,6 +10108,7 @@
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="F1:G1"/>
+    <mergeCell ref="R1:S1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9133,13 +10120,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="39" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -9153,6 +10140,8 @@
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9203,11 +10192,17 @@
         </is>
       </c>
       <c r="Q1" s="2" t="n"/>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>최종</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="D2" t="inlineStr">
         <is>
-          <t>대학의 마감일에는 10시, 14시, 15시, 최종해주시면 됩니다.</t>
+          <t>2027 수시모집 최종 경쟁률 마감 현황</t>
         </is>
       </c>
     </row>
@@ -9295,6 +10290,16 @@
         </is>
       </c>
       <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t>경쟁률</t>
+        </is>
+      </c>
+      <c r="Q4" s="4" t="inlineStr">
+        <is>
+          <t>지원인원</t>
+        </is>
+      </c>
+      <c r="R4" s="4" t="inlineStr">
         <is>
           <t>경쟁률</t>
         </is>
@@ -9357,6 +10362,8 @@
       <c r="N5" s="8" t="inlineStr"/>
       <c r="O5" s="8" t="inlineStr"/>
       <c r="P5" s="8" t="inlineStr"/>
+      <c r="Q5" s="8" t="inlineStr"/>
+      <c r="R5" s="8" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -9415,6 +10422,8 @@
       <c r="N6" s="8" t="inlineStr"/>
       <c r="O6" s="8" t="inlineStr"/>
       <c r="P6" s="8" t="inlineStr"/>
+      <c r="Q6" s="8" t="inlineStr"/>
+      <c r="R6" s="8" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -9473,9 +10482,11 @@
       <c r="N7" s="6" t="inlineStr"/>
       <c r="O7" s="6" t="inlineStr"/>
       <c r="P7" s="6" t="inlineStr"/>
+      <c r="Q7" s="6" t="inlineStr"/>
+      <c r="R7" s="6" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="N1:O1"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="D1:E1"/>
@@ -9484,6 +10495,7 @@
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="F1:G1"/>
+    <mergeCell ref="R1:S1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9495,13 +10507,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q63"/>
+  <dimension ref="A1:S63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="39" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -9515,6 +10527,8 @@
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9565,11 +10579,17 @@
         </is>
       </c>
       <c r="Q1" s="2" t="n"/>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>최종</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="D2" t="inlineStr">
         <is>
-          <t>대학의 마감일에는 10시, 14시, 15시, 최종해주시면 됩니다.</t>
+          <t>2027 수시모집 최종 경쟁률 마감 현황</t>
         </is>
       </c>
     </row>
@@ -9661,6 +10681,16 @@
           <t>경쟁률</t>
         </is>
       </c>
+      <c r="Q4" s="4" t="inlineStr">
+        <is>
+          <t>지원인원</t>
+        </is>
+      </c>
+      <c r="R4" s="4" t="inlineStr">
+        <is>
+          <t>경쟁률</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -9743,6 +10773,16 @@
           <t>6.89 : 1</t>
         </is>
       </c>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>1,926</t>
+        </is>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>7.08 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -9832,6 +10872,16 @@
           <t>경쟁률</t>
         </is>
       </c>
+      <c r="Q7" s="4" t="inlineStr">
+        <is>
+          <t>지원인원</t>
+        </is>
+      </c>
+      <c r="R7" s="4" t="inlineStr">
+        <is>
+          <t>경쟁률</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -9914,6 +10964,16 @@
           <t>4.60 : 1</t>
         </is>
       </c>
+      <c r="Q8" s="8" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="R8" s="8" t="inlineStr">
+        <is>
+          <t>4.78 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -9996,6 +11056,16 @@
           <t>6.80 : 1</t>
         </is>
       </c>
+      <c r="Q9" s="8" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="R9" s="8" t="inlineStr">
+        <is>
+          <t>7.20 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -10078,6 +11148,16 @@
           <t>16.53 : 1</t>
         </is>
       </c>
+      <c r="Q10" s="8" t="inlineStr">
+        <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="R10" s="8" t="inlineStr">
+        <is>
+          <t>16.98 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -10160,6 +11240,16 @@
           <t>17.29 : 1</t>
         </is>
       </c>
+      <c r="Q11" s="8" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="R11" s="8" t="inlineStr">
+        <is>
+          <t>17.29 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -10242,6 +11332,16 @@
           <t>9.50 : 1</t>
         </is>
       </c>
+      <c r="Q12" s="8" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="R12" s="8" t="inlineStr">
+        <is>
+          <t>9.50 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -10324,6 +11424,16 @@
           <t>3.22 : 1</t>
         </is>
       </c>
+      <c r="Q13" s="8" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="R13" s="8" t="inlineStr">
+        <is>
+          <t>3.22 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -10406,6 +11516,16 @@
           <t>2.50 : 1</t>
         </is>
       </c>
+      <c r="Q14" s="8" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="R14" s="8" t="inlineStr">
+        <is>
+          <t>2.50 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
@@ -10488,6 +11608,16 @@
           <t>3.50 : 1</t>
         </is>
       </c>
+      <c r="Q15" s="8" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="R15" s="8" t="inlineStr">
+        <is>
+          <t>3.70 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
@@ -10570,6 +11700,16 @@
           <t>4.57 : 1</t>
         </is>
       </c>
+      <c r="Q16" s="8" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="R16" s="8" t="inlineStr">
+        <is>
+          <t>4.71 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
@@ -10652,6 +11792,16 @@
           <t>1.80 : 1</t>
         </is>
       </c>
+      <c r="Q17" s="8" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R17" s="8" t="inlineStr">
+        <is>
+          <t>1.90 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
@@ -10734,6 +11884,16 @@
           <t>7.50 : 1</t>
         </is>
       </c>
+      <c r="Q18" s="8" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="R18" s="8" t="inlineStr">
+        <is>
+          <t>8.00 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -10816,6 +11976,16 @@
           <t>6.89 : 1</t>
         </is>
       </c>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>1,926</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>7.08 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -10905,6 +12075,16 @@
           <t>경쟁률</t>
         </is>
       </c>
+      <c r="Q21" s="4" t="inlineStr">
+        <is>
+          <t>지원인원</t>
+        </is>
+      </c>
+      <c r="R21" s="4" t="inlineStr">
+        <is>
+          <t>경쟁률</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
@@ -10987,6 +12167,16 @@
           <t>4.60 : 1</t>
         </is>
       </c>
+      <c r="Q22" s="8" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="R22" s="8" t="inlineStr">
+        <is>
+          <t>4.78 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
@@ -11069,6 +12259,16 @@
           <t>4.60 : 1</t>
         </is>
       </c>
+      <c r="Q23" s="8" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="R23" s="8" t="inlineStr">
+        <is>
+          <t>4.78 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -11158,6 +12358,16 @@
           <t>경쟁률</t>
         </is>
       </c>
+      <c r="Q25" s="4" t="inlineStr">
+        <is>
+          <t>지원인원</t>
+        </is>
+      </c>
+      <c r="R25" s="4" t="inlineStr">
+        <is>
+          <t>경쟁률</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
@@ -11240,6 +12450,16 @@
           <t>6.80 : 1</t>
         </is>
       </c>
+      <c r="Q26" s="8" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="R26" s="8" t="inlineStr">
+        <is>
+          <t>7.20 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
@@ -11322,6 +12542,16 @@
           <t>6.80 : 1</t>
         </is>
       </c>
+      <c r="Q27" s="8" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="R27" s="8" t="inlineStr">
+        <is>
+          <t>7.20 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -11411,6 +12641,16 @@
           <t>경쟁률</t>
         </is>
       </c>
+      <c r="Q29" s="4" t="inlineStr">
+        <is>
+          <t>지원인원</t>
+        </is>
+      </c>
+      <c r="R29" s="4" t="inlineStr">
+        <is>
+          <t>경쟁률</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
@@ -11493,6 +12733,16 @@
           <t>16.53 : 1</t>
         </is>
       </c>
+      <c r="Q30" s="8" t="inlineStr">
+        <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="R30" s="8" t="inlineStr">
+        <is>
+          <t>16.98 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
@@ -11575,6 +12825,16 @@
           <t>16.53 : 1</t>
         </is>
       </c>
+      <c r="Q31" s="8" t="inlineStr">
+        <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="R31" s="8" t="inlineStr">
+        <is>
+          <t>16.98 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -11664,6 +12924,16 @@
           <t>경쟁률</t>
         </is>
       </c>
+      <c r="Q33" s="4" t="inlineStr">
+        <is>
+          <t>지원인원</t>
+        </is>
+      </c>
+      <c r="R33" s="4" t="inlineStr">
+        <is>
+          <t>경쟁률</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
@@ -11746,6 +13016,16 @@
           <t>17.29 : 1</t>
         </is>
       </c>
+      <c r="Q34" s="8" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="R34" s="8" t="inlineStr">
+        <is>
+          <t>17.29 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
@@ -11828,6 +13108,16 @@
           <t>17.29 : 1</t>
         </is>
       </c>
+      <c r="Q35" s="8" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="R35" s="8" t="inlineStr">
+        <is>
+          <t>17.29 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
@@ -11917,6 +13207,16 @@
           <t>경쟁률</t>
         </is>
       </c>
+      <c r="Q37" s="4" t="inlineStr">
+        <is>
+          <t>지원인원</t>
+        </is>
+      </c>
+      <c r="R37" s="4" t="inlineStr">
+        <is>
+          <t>경쟁률</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
@@ -11999,6 +13299,16 @@
           <t>9.50 : 1</t>
         </is>
       </c>
+      <c r="Q38" s="8" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="R38" s="8" t="inlineStr">
+        <is>
+          <t>9.50 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
@@ -12081,6 +13391,16 @@
           <t>9.50 : 1</t>
         </is>
       </c>
+      <c r="Q39" s="8" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="R39" s="8" t="inlineStr">
+        <is>
+          <t>9.50 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
@@ -12170,6 +13490,16 @@
           <t>경쟁률</t>
         </is>
       </c>
+      <c r="Q41" s="4" t="inlineStr">
+        <is>
+          <t>지원인원</t>
+        </is>
+      </c>
+      <c r="R41" s="4" t="inlineStr">
+        <is>
+          <t>경쟁률</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
@@ -12252,6 +13582,16 @@
           <t>3.22 : 1</t>
         </is>
       </c>
+      <c r="Q42" s="8" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="R42" s="8" t="inlineStr">
+        <is>
+          <t>3.22 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
@@ -12334,6 +13674,16 @@
           <t>3.22 : 1</t>
         </is>
       </c>
+      <c r="Q43" s="8" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="R43" s="8" t="inlineStr">
+        <is>
+          <t>3.22 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -12423,6 +13773,16 @@
           <t>경쟁률</t>
         </is>
       </c>
+      <c r="Q45" s="4" t="inlineStr">
+        <is>
+          <t>지원인원</t>
+        </is>
+      </c>
+      <c r="R45" s="4" t="inlineStr">
+        <is>
+          <t>경쟁률</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
@@ -12505,6 +13865,16 @@
           <t>2.50 : 1</t>
         </is>
       </c>
+      <c r="Q46" s="8" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="R46" s="8" t="inlineStr">
+        <is>
+          <t>2.50 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
@@ -12587,6 +13957,16 @@
           <t>2.50 : 1</t>
         </is>
       </c>
+      <c r="Q47" s="8" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="R47" s="8" t="inlineStr">
+        <is>
+          <t>2.50 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
@@ -12676,6 +14056,16 @@
           <t>경쟁률</t>
         </is>
       </c>
+      <c r="Q49" s="4" t="inlineStr">
+        <is>
+          <t>지원인원</t>
+        </is>
+      </c>
+      <c r="R49" s="4" t="inlineStr">
+        <is>
+          <t>경쟁률</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
@@ -12758,6 +14148,16 @@
           <t>3.50 : 1</t>
         </is>
       </c>
+      <c r="Q50" s="8" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="R50" s="8" t="inlineStr">
+        <is>
+          <t>3.70 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
@@ -12840,6 +14240,16 @@
           <t>3.50 : 1</t>
         </is>
       </c>
+      <c r="Q51" s="8" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="R51" s="8" t="inlineStr">
+        <is>
+          <t>3.70 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
@@ -12929,6 +14339,16 @@
           <t>경쟁률</t>
         </is>
       </c>
+      <c r="Q53" s="4" t="inlineStr">
+        <is>
+          <t>지원인원</t>
+        </is>
+      </c>
+      <c r="R53" s="4" t="inlineStr">
+        <is>
+          <t>경쟁률</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
@@ -13011,6 +14431,16 @@
           <t>4.57 : 1</t>
         </is>
       </c>
+      <c r="Q54" s="8" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="R54" s="8" t="inlineStr">
+        <is>
+          <t>4.71 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
@@ -13093,6 +14523,16 @@
           <t>4.57 : 1</t>
         </is>
       </c>
+      <c r="Q55" s="8" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="R55" s="8" t="inlineStr">
+        <is>
+          <t>4.71 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
@@ -13182,6 +14622,16 @@
           <t>경쟁률</t>
         </is>
       </c>
+      <c r="Q57" s="4" t="inlineStr">
+        <is>
+          <t>지원인원</t>
+        </is>
+      </c>
+      <c r="R57" s="4" t="inlineStr">
+        <is>
+          <t>경쟁률</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
@@ -13264,6 +14714,16 @@
           <t>1.80 : 1</t>
         </is>
       </c>
+      <c r="Q58" s="8" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R58" s="8" t="inlineStr">
+        <is>
+          <t>1.90 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
@@ -13346,6 +14806,16 @@
           <t>1.80 : 1</t>
         </is>
       </c>
+      <c r="Q59" s="8" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R59" s="8" t="inlineStr">
+        <is>
+          <t>1.90 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
@@ -13435,6 +14905,16 @@
           <t>경쟁률</t>
         </is>
       </c>
+      <c r="Q61" s="4" t="inlineStr">
+        <is>
+          <t>지원인원</t>
+        </is>
+      </c>
+      <c r="R61" s="4" t="inlineStr">
+        <is>
+          <t>경쟁률</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
@@ -13517,6 +14997,16 @@
           <t>7.50 : 1</t>
         </is>
       </c>
+      <c r="Q62" s="8" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="R62" s="8" t="inlineStr">
+        <is>
+          <t>8.00 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
@@ -13599,9 +15089,19 @@
           <t>7.50 : 1</t>
         </is>
       </c>
+      <c r="Q63" s="8" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="R63" s="8" t="inlineStr">
+        <is>
+          <t>8.00 : 1</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="N1:O1"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="D1:E1"/>
@@ -13610,6 +15110,7 @@
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="F1:G1"/>
+    <mergeCell ref="R1:S1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13621,13 +15122,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q56"/>
+  <dimension ref="A1:S56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="39" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
@@ -13641,6 +15142,8 @@
     <col width="12" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13691,11 +15194,17 @@
         </is>
       </c>
       <c r="Q1" s="2" t="n"/>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>최종</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="D2" t="inlineStr">
         <is>
-          <t>대학의 마감일에는 10시, 14시, 15시, 최종해주시면 됩니다.</t>
+          <t>2027 수시모집 최종 경쟁률 마감 현황</t>
         </is>
       </c>
     </row>
@@ -13787,6 +15296,16 @@
           <t>경쟁률</t>
         </is>
       </c>
+      <c r="Q4" s="4" t="inlineStr">
+        <is>
+          <t>지원인원</t>
+        </is>
+      </c>
+      <c r="R4" s="4" t="inlineStr">
+        <is>
+          <t>경쟁률</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -13869,6 +15388,16 @@
           <t>4.48 : 1</t>
         </is>
       </c>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>1,519</t>
+        </is>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>4.90 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -13958,6 +15487,16 @@
           <t>경쟁률</t>
         </is>
       </c>
+      <c r="Q7" s="4" t="inlineStr">
+        <is>
+          <t>지원인원</t>
+        </is>
+      </c>
+      <c r="R7" s="4" t="inlineStr">
+        <is>
+          <t>경쟁률</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -14040,6 +15579,16 @@
           <t>10.64 : 1</t>
         </is>
       </c>
+      <c r="Q8" s="8" t="inlineStr">
+        <is>
+          <t>593</t>
+        </is>
+      </c>
+      <c r="R8" s="8" t="inlineStr">
+        <is>
+          <t>11.86 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -14122,6 +15671,16 @@
           <t>3.58 : 1</t>
         </is>
       </c>
+      <c r="Q9" s="8" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="R9" s="8" t="inlineStr">
+        <is>
+          <t>3.89 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -14204,6 +15763,16 @@
           <t>2.60 : 1</t>
         </is>
       </c>
+      <c r="Q10" s="8" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="R10" s="8" t="inlineStr">
+        <is>
+          <t>2.75 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -14286,6 +15855,16 @@
           <t>6.00 : 1</t>
         </is>
       </c>
+      <c r="Q11" s="8" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="R11" s="8" t="inlineStr">
+        <is>
+          <t>7.33 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -14368,6 +15947,16 @@
           <t>6.00 : 1</t>
         </is>
       </c>
+      <c r="Q12" s="8" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="R12" s="8" t="inlineStr">
+        <is>
+          <t>6.33 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -14450,6 +16039,16 @@
           <t>7.50 : 1</t>
         </is>
       </c>
+      <c r="Q13" s="8" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="R13" s="8" t="inlineStr">
+        <is>
+          <t>8.17 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -14532,6 +16131,16 @@
           <t>5.53 : 1</t>
         </is>
       </c>
+      <c r="Q14" s="8" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="R14" s="8" t="inlineStr">
+        <is>
+          <t>6.33 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
@@ -14614,6 +16223,16 @@
           <t>2.10 : 1</t>
         </is>
       </c>
+      <c r="Q15" s="8" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="R15" s="8" t="inlineStr">
+        <is>
+          <t>2.20 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
@@ -14696,6 +16315,16 @@
           <t>0.33 : 1</t>
         </is>
       </c>
+      <c r="Q16" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" s="8" t="inlineStr">
+        <is>
+          <t>0.33 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -14778,6 +16407,16 @@
           <t>4.48 : 1</t>
         </is>
       </c>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>1,519</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>4.90 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -14872,6 +16511,16 @@
           <t>경쟁률</t>
         </is>
       </c>
+      <c r="R19" s="4" t="inlineStr">
+        <is>
+          <t>지원인원</t>
+        </is>
+      </c>
+      <c r="S19" s="4" t="inlineStr">
+        <is>
+          <t>경쟁률</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
@@ -14959,6 +16608,16 @@
           <t>10.64 : 1</t>
         </is>
       </c>
+      <c r="R20" s="8" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="S20" s="8" t="inlineStr">
+        <is>
+          <t>11.86 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
@@ -15014,6 +16673,12 @@
         </is>
       </c>
       <c r="Q21" s="8" t="inlineStr"/>
+      <c r="R21" s="8" t="inlineStr">
+        <is>
+          <t>362</t>
+        </is>
+      </c>
+      <c r="S21" s="8" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
@@ -15097,6 +16762,16 @@
           <t>10.64 : 1</t>
         </is>
       </c>
+      <c r="R22" s="8" t="inlineStr">
+        <is>
+          <t>593</t>
+        </is>
+      </c>
+      <c r="S22" s="8" t="inlineStr">
+        <is>
+          <t>11.86 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -15191,6 +16866,16 @@
           <t>경쟁률</t>
         </is>
       </c>
+      <c r="R24" s="4" t="inlineStr">
+        <is>
+          <t>지원인원</t>
+        </is>
+      </c>
+      <c r="S24" s="4" t="inlineStr">
+        <is>
+          <t>경쟁률</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
@@ -15278,6 +16963,16 @@
           <t>3.58 : 1</t>
         </is>
       </c>
+      <c r="R25" s="8" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="S25" s="8" t="inlineStr">
+        <is>
+          <t>3.89 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
@@ -15333,6 +17028,12 @@
         </is>
       </c>
       <c r="Q26" s="8" t="inlineStr"/>
+      <c r="R26" s="8" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="S26" s="8" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
@@ -15416,6 +17117,16 @@
           <t>3.58 : 1</t>
         </is>
       </c>
+      <c r="R27" s="8" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="S27" s="8" t="inlineStr">
+        <is>
+          <t>3.89 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -15510,6 +17221,16 @@
           <t>경쟁률</t>
         </is>
       </c>
+      <c r="R29" s="4" t="inlineStr">
+        <is>
+          <t>지원인원</t>
+        </is>
+      </c>
+      <c r="S29" s="4" t="inlineStr">
+        <is>
+          <t>경쟁률</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
@@ -15597,6 +17318,16 @@
           <t>2.60 : 1</t>
         </is>
       </c>
+      <c r="R30" s="8" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="S30" s="8" t="inlineStr">
+        <is>
+          <t>2.75 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
@@ -15652,6 +17383,12 @@
         </is>
       </c>
       <c r="Q31" s="8" t="inlineStr"/>
+      <c r="R31" s="8" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="S31" s="8" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
@@ -15735,6 +17472,16 @@
           <t>2.60 : 1</t>
         </is>
       </c>
+      <c r="R32" s="8" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="S32" s="8" t="inlineStr">
+        <is>
+          <t>2.75 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
@@ -15824,6 +17571,16 @@
           <t>경쟁률</t>
         </is>
       </c>
+      <c r="Q34" s="4" t="inlineStr">
+        <is>
+          <t>지원인원</t>
+        </is>
+      </c>
+      <c r="R34" s="4" t="inlineStr">
+        <is>
+          <t>경쟁률</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
@@ -15906,6 +17663,16 @@
           <t>6.00 : 1</t>
         </is>
       </c>
+      <c r="Q35" s="8" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="R35" s="8" t="inlineStr">
+        <is>
+          <t>7.33 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
@@ -15988,6 +17755,16 @@
           <t>6.00 : 1</t>
         </is>
       </c>
+      <c r="Q36" s="8" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="R36" s="8" t="inlineStr">
+        <is>
+          <t>7.33 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -16077,6 +17854,16 @@
           <t>경쟁률</t>
         </is>
       </c>
+      <c r="Q38" s="4" t="inlineStr">
+        <is>
+          <t>지원인원</t>
+        </is>
+      </c>
+      <c r="R38" s="4" t="inlineStr">
+        <is>
+          <t>경쟁률</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
@@ -16159,6 +17946,16 @@
           <t>6.00 : 1</t>
         </is>
       </c>
+      <c r="Q39" s="8" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="R39" s="8" t="inlineStr">
+        <is>
+          <t>6.33 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
@@ -16241,6 +18038,16 @@
           <t>6.00 : 1</t>
         </is>
       </c>
+      <c r="Q40" s="8" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="R40" s="8" t="inlineStr">
+        <is>
+          <t>6.33 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -16330,6 +18137,16 @@
           <t>경쟁률</t>
         </is>
       </c>
+      <c r="Q42" s="4" t="inlineStr">
+        <is>
+          <t>지원인원</t>
+        </is>
+      </c>
+      <c r="R42" s="4" t="inlineStr">
+        <is>
+          <t>경쟁률</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
@@ -16412,6 +18229,16 @@
           <t>7.50 : 1</t>
         </is>
       </c>
+      <c r="Q43" s="8" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="R43" s="8" t="inlineStr">
+        <is>
+          <t>8.17 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
@@ -16494,6 +18321,16 @@
           <t>7.50 : 1</t>
         </is>
       </c>
+      <c r="Q44" s="8" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="R44" s="8" t="inlineStr">
+        <is>
+          <t>8.17 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -16583,6 +18420,16 @@
           <t>경쟁률</t>
         </is>
       </c>
+      <c r="Q46" s="4" t="inlineStr">
+        <is>
+          <t>지원인원</t>
+        </is>
+      </c>
+      <c r="R46" s="4" t="inlineStr">
+        <is>
+          <t>경쟁률</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
@@ -16665,6 +18512,16 @@
           <t>5.53 : 1</t>
         </is>
       </c>
+      <c r="Q47" s="8" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="R47" s="8" t="inlineStr">
+        <is>
+          <t>6.33 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
@@ -16747,6 +18604,16 @@
           <t>5.53 : 1</t>
         </is>
       </c>
+      <c r="Q48" s="8" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="R48" s="8" t="inlineStr">
+        <is>
+          <t>6.33 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
@@ -16836,6 +18703,16 @@
           <t>경쟁률</t>
         </is>
       </c>
+      <c r="Q50" s="4" t="inlineStr">
+        <is>
+          <t>지원인원</t>
+        </is>
+      </c>
+      <c r="R50" s="4" t="inlineStr">
+        <is>
+          <t>경쟁률</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
@@ -16918,6 +18795,16 @@
           <t>2.10 : 1</t>
         </is>
       </c>
+      <c r="Q51" s="8" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="R51" s="8" t="inlineStr">
+        <is>
+          <t>2.20 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
@@ -17000,6 +18887,16 @@
           <t>2.10 : 1</t>
         </is>
       </c>
+      <c r="Q52" s="8" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="R52" s="8" t="inlineStr">
+        <is>
+          <t>2.20 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
@@ -17089,6 +18986,16 @@
           <t>경쟁률</t>
         </is>
       </c>
+      <c r="Q54" s="4" t="inlineStr">
+        <is>
+          <t>지원인원</t>
+        </is>
+      </c>
+      <c r="R54" s="4" t="inlineStr">
+        <is>
+          <t>경쟁률</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
@@ -17171,6 +19078,16 @@
           <t>0.33 : 1</t>
         </is>
       </c>
+      <c r="Q55" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R55" s="8" t="inlineStr">
+        <is>
+          <t>0.33 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
@@ -17253,9 +19170,19 @@
           <t>0.33 : 1</t>
         </is>
       </c>
+      <c r="Q56" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R56" s="8" t="inlineStr">
+        <is>
+          <t>0.33 : 1</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="N1:O1"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="D1:E1"/>
@@ -17264,6 +19191,7 @@
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="F1:G1"/>
+    <mergeCell ref="R1:S1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17275,13 +19203,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:S11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="39" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -17295,6 +19223,8 @@
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17345,11 +19275,17 @@
         </is>
       </c>
       <c r="Q1" s="2" t="n"/>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>최종</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="D2" t="inlineStr">
         <is>
-          <t>대학의 마감일에는 10시, 14시, 15시, 최종해주시면 됩니다.</t>
+          <t>2027 수시모집 최종 경쟁률 마감 현황</t>
         </is>
       </c>
     </row>
@@ -17441,6 +19377,16 @@
           <t>경쟁률</t>
         </is>
       </c>
+      <c r="Q4" s="4" t="inlineStr">
+        <is>
+          <t>지원인원</t>
+        </is>
+      </c>
+      <c r="R4" s="4" t="inlineStr">
+        <is>
+          <t>경쟁률</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
@@ -17523,6 +19469,16 @@
           <t>7.52 : 1</t>
         </is>
       </c>
+      <c r="Q5" s="8" t="inlineStr">
+        <is>
+          <t>534</t>
+        </is>
+      </c>
+      <c r="R5" s="8" t="inlineStr">
+        <is>
+          <t>8.22 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -17605,6 +19561,16 @@
           <t>4.71 : 1</t>
         </is>
       </c>
+      <c r="Q6" s="8" t="inlineStr">
+        <is>
+          <t>623</t>
+        </is>
+      </c>
+      <c r="R6" s="8" t="inlineStr">
+        <is>
+          <t>4.98 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -17687,6 +19653,16 @@
           <t>4.33 : 1</t>
         </is>
       </c>
+      <c r="Q7" s="8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R7" s="8" t="inlineStr">
+        <is>
+          <t>5.00 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -17769,6 +19745,16 @@
           <t>5.33 : 1</t>
         </is>
       </c>
+      <c r="Q8" s="8" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="R8" s="8" t="inlineStr">
+        <is>
+          <t>5.50 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -17851,6 +19837,16 @@
           <t>2.92 : 1</t>
         </is>
       </c>
+      <c r="Q9" s="8" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="R9" s="8" t="inlineStr">
+        <is>
+          <t>3.00 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -17933,6 +19929,16 @@
           <t>8.60 : 1</t>
         </is>
       </c>
+      <c r="Q10" s="8" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="R10" s="8" t="inlineStr">
+        <is>
+          <t>9.60 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -18015,9 +20021,19 @@
           <t>5.55 : 1</t>
         </is>
       </c>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>1,322</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>5.95 : 1</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="N1:O1"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="D1:E1"/>
@@ -18026,6 +20042,7 @@
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="F1:G1"/>
+    <mergeCell ref="R1:S1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18037,13 +20054,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="39" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -18057,6 +20074,8 @@
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18107,11 +20126,17 @@
         </is>
       </c>
       <c r="Q1" s="2" t="n"/>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>최종</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="D2" t="inlineStr">
         <is>
-          <t>대학의 마감일에는 10시, 14시, 15시, 최종해주시면 됩니다.</t>
+          <t>2027 수시모집 최종 경쟁률 마감 현황</t>
         </is>
       </c>
     </row>
@@ -18199,6 +20224,16 @@
         </is>
       </c>
       <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t>경쟁률</t>
+        </is>
+      </c>
+      <c r="Q4" s="4" t="inlineStr">
+        <is>
+          <t>지원인원</t>
+        </is>
+      </c>
+      <c r="R4" s="4" t="inlineStr">
         <is>
           <t>경쟁률</t>
         </is>
@@ -18261,6 +20296,8 @@
       <c r="N5" s="8" t="inlineStr"/>
       <c r="O5" s="8" t="inlineStr"/>
       <c r="P5" s="8" t="inlineStr"/>
+      <c r="Q5" s="8" t="inlineStr"/>
+      <c r="R5" s="8" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -18319,6 +20356,8 @@
       <c r="N6" s="8" t="inlineStr"/>
       <c r="O6" s="8" t="inlineStr"/>
       <c r="P6" s="8" t="inlineStr"/>
+      <c r="Q6" s="8" t="inlineStr"/>
+      <c r="R6" s="8" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -18377,9 +20416,11 @@
       <c r="N7" s="6" t="inlineStr"/>
       <c r="O7" s="6" t="inlineStr"/>
       <c r="P7" s="6" t="inlineStr"/>
+      <c r="Q7" s="6" t="inlineStr"/>
+      <c r="R7" s="6" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="N1:O1"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="D1:E1"/>
@@ -18388,6 +20429,7 @@
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="F1:G1"/>
+    <mergeCell ref="R1:S1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18399,13 +20441,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:S12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="39" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -18419,6 +20461,8 @@
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18469,11 +20513,17 @@
         </is>
       </c>
       <c r="Q1" s="2" t="n"/>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>최종</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="D2" t="inlineStr">
         <is>
-          <t>대학의 마감일에는 10시, 14시, 15시, 최종해주시면 됩니다.</t>
+          <t>2027 수시모집 최종 경쟁률 마감 현황</t>
         </is>
       </c>
     </row>
@@ -18565,6 +20615,16 @@
           <t>경쟁률</t>
         </is>
       </c>
+      <c r="Q4" s="4" t="inlineStr">
+        <is>
+          <t>지원인원</t>
+        </is>
+      </c>
+      <c r="R4" s="4" t="inlineStr">
+        <is>
+          <t>경쟁률</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
@@ -18647,6 +20707,16 @@
           <t>19.33 : 1</t>
         </is>
       </c>
+      <c r="Q5" s="8" t="inlineStr">
+        <is>
+          <t>928</t>
+        </is>
+      </c>
+      <c r="R5" s="8" t="inlineStr">
+        <is>
+          <t>19.33 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -18729,6 +20799,16 @@
           <t>3.54 : 1</t>
         </is>
       </c>
+      <c r="Q6" s="8" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="R6" s="8" t="inlineStr">
+        <is>
+          <t>3.54 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -18811,6 +20891,16 @@
           <t>6.60 : 1</t>
         </is>
       </c>
+      <c r="Q7" s="8" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="R7" s="8" t="inlineStr">
+        <is>
+          <t>6.60 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -18893,6 +20983,16 @@
           <t>5.00 : 1</t>
         </is>
       </c>
+      <c r="Q8" s="8" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="R8" s="8" t="inlineStr">
+        <is>
+          <t>5.00 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -18975,6 +21075,16 @@
           <t>11.64 : 1</t>
         </is>
       </c>
+      <c r="Q9" s="8" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="R9" s="8" t="inlineStr">
+        <is>
+          <t>11.64 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -19057,6 +21167,16 @@
           <t>12.00 : 1</t>
         </is>
       </c>
+      <c r="Q10" s="8" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="R10" s="8" t="inlineStr">
+        <is>
+          <t>12.00 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -19139,6 +21259,16 @@
           <t>2.25 : 1</t>
         </is>
       </c>
+      <c r="Q11" s="8" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R11" s="8" t="inlineStr">
+        <is>
+          <t>2.25 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -19221,9 +21351,19 @@
           <t>8.12 : 1</t>
         </is>
       </c>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>1,583</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>8.12 : 1</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="N1:O1"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="D1:E1"/>
@@ -19232,6 +21372,7 @@
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="F1:G1"/>
+    <mergeCell ref="R1:S1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19243,13 +21384,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q38"/>
+  <dimension ref="A1:S38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="39" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -19263,6 +21404,8 @@
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19313,11 +21456,17 @@
         </is>
       </c>
       <c r="Q1" s="2" t="n"/>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>최종</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="D2" t="inlineStr">
         <is>
-          <t>대학의 마감일에는 10시, 14시, 15시, 최종해주시면 됩니다.</t>
+          <t>2027 수시모집 최종 경쟁률 마감 현황</t>
         </is>
       </c>
     </row>
@@ -19409,6 +21558,16 @@
           <t>경쟁률</t>
         </is>
       </c>
+      <c r="Q4" s="4" t="inlineStr">
+        <is>
+          <t>지원인원</t>
+        </is>
+      </c>
+      <c r="R4" s="4" t="inlineStr">
+        <is>
+          <t>경쟁률</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
@@ -19491,6 +21650,16 @@
           <t>15.44 : 1</t>
         </is>
       </c>
+      <c r="Q5" s="8" t="inlineStr">
+        <is>
+          <t>814</t>
+        </is>
+      </c>
+      <c r="R5" s="8" t="inlineStr">
+        <is>
+          <t>16.28 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -19573,6 +21742,16 @@
           <t>5.63 : 1</t>
         </is>
       </c>
+      <c r="Q6" s="8" t="inlineStr">
+        <is>
+          <t>717</t>
+        </is>
+      </c>
+      <c r="R6" s="8" t="inlineStr">
+        <is>
+          <t>5.83 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -19655,6 +21834,16 @@
           <t>8.67 : 1</t>
         </is>
       </c>
+      <c r="Q7" s="8" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="R7" s="8" t="inlineStr">
+        <is>
+          <t>8.67 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -19737,6 +21926,16 @@
           <t>6.67 : 1</t>
         </is>
       </c>
+      <c r="Q8" s="8" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="R8" s="8" t="inlineStr">
+        <is>
+          <t>7.33 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -19819,6 +22018,16 @@
           <t>15.58 : 1</t>
         </is>
       </c>
+      <c r="Q9" s="8" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="R9" s="8" t="inlineStr">
+        <is>
+          <t>16.08 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -19901,6 +22110,16 @@
           <t>10.40 : 1</t>
         </is>
       </c>
+      <c r="Q10" s="8" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="R10" s="8" t="inlineStr">
+        <is>
+          <t>11.40 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -19983,6 +22202,16 @@
           <t>1.42 : 1</t>
         </is>
       </c>
+      <c r="Q11" s="8" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R11" s="8" t="inlineStr">
+        <is>
+          <t>1.50 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -20065,6 +22294,16 @@
           <t>4.65 : 1</t>
         </is>
       </c>
+      <c r="Q12" s="8" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="R12" s="8" t="inlineStr">
+        <is>
+          <t>4.95 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -20147,6 +22386,16 @@
           <t>8.15 : 1</t>
         </is>
       </c>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>1,946</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>8.54 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -20236,6 +22485,16 @@
           <t>경쟁률</t>
         </is>
       </c>
+      <c r="Q15" s="4" t="inlineStr">
+        <is>
+          <t>지원인원</t>
+        </is>
+      </c>
+      <c r="R15" s="4" t="inlineStr">
+        <is>
+          <t>경쟁률</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
@@ -20318,6 +22577,16 @@
           <t>15.44 : 1</t>
         </is>
       </c>
+      <c r="Q16" s="8" t="inlineStr">
+        <is>
+          <t>814</t>
+        </is>
+      </c>
+      <c r="R16" s="8" t="inlineStr">
+        <is>
+          <t>16.28 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -20407,6 +22676,16 @@
           <t>경쟁률</t>
         </is>
       </c>
+      <c r="Q18" s="4" t="inlineStr">
+        <is>
+          <t>지원인원</t>
+        </is>
+      </c>
+      <c r="R18" s="4" t="inlineStr">
+        <is>
+          <t>경쟁률</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
@@ -20489,6 +22768,16 @@
           <t>5.63 : 1</t>
         </is>
       </c>
+      <c r="Q19" s="8" t="inlineStr">
+        <is>
+          <t>717</t>
+        </is>
+      </c>
+      <c r="R19" s="8" t="inlineStr">
+        <is>
+          <t>5.83 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -20578,6 +22867,16 @@
           <t>경쟁률</t>
         </is>
       </c>
+      <c r="Q21" s="4" t="inlineStr">
+        <is>
+          <t>지원인원</t>
+        </is>
+      </c>
+      <c r="R21" s="4" t="inlineStr">
+        <is>
+          <t>경쟁률</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
@@ -20660,6 +22959,16 @@
           <t>8.67 : 1</t>
         </is>
       </c>
+      <c r="Q22" s="8" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="R22" s="8" t="inlineStr">
+        <is>
+          <t>8.67 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -20749,6 +23058,16 @@
           <t>경쟁률</t>
         </is>
       </c>
+      <c r="Q24" s="4" t="inlineStr">
+        <is>
+          <t>지원인원</t>
+        </is>
+      </c>
+      <c r="R24" s="4" t="inlineStr">
+        <is>
+          <t>경쟁률</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
@@ -20831,6 +23150,16 @@
           <t>6.67 : 1</t>
         </is>
       </c>
+      <c r="Q25" s="8" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="R25" s="8" t="inlineStr">
+        <is>
+          <t>7.33 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -20920,6 +23249,16 @@
           <t>경쟁률</t>
         </is>
       </c>
+      <c r="Q27" s="4" t="inlineStr">
+        <is>
+          <t>지원인원</t>
+        </is>
+      </c>
+      <c r="R27" s="4" t="inlineStr">
+        <is>
+          <t>경쟁률</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
@@ -21002,6 +23341,16 @@
           <t>15.58 : 1</t>
         </is>
       </c>
+      <c r="Q28" s="8" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="R28" s="8" t="inlineStr">
+        <is>
+          <t>16.08 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -21091,6 +23440,16 @@
           <t>경쟁률</t>
         </is>
       </c>
+      <c r="Q30" s="4" t="inlineStr">
+        <is>
+          <t>지원인원</t>
+        </is>
+      </c>
+      <c r="R30" s="4" t="inlineStr">
+        <is>
+          <t>경쟁률</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
@@ -21173,6 +23532,16 @@
           <t>10.40 : 1</t>
         </is>
       </c>
+      <c r="Q31" s="8" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="R31" s="8" t="inlineStr">
+        <is>
+          <t>11.40 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -21262,6 +23631,16 @@
           <t>경쟁률</t>
         </is>
       </c>
+      <c r="Q33" s="4" t="inlineStr">
+        <is>
+          <t>지원인원</t>
+        </is>
+      </c>
+      <c r="R33" s="4" t="inlineStr">
+        <is>
+          <t>경쟁률</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
@@ -21344,6 +23723,16 @@
           <t>1.42 : 1</t>
         </is>
       </c>
+      <c r="Q34" s="8" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R34" s="8" t="inlineStr">
+        <is>
+          <t>1.50 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
@@ -21433,6 +23822,16 @@
           <t>경쟁률</t>
         </is>
       </c>
+      <c r="Q36" s="4" t="inlineStr">
+        <is>
+          <t>지원인원</t>
+        </is>
+      </c>
+      <c r="R36" s="4" t="inlineStr">
+        <is>
+          <t>경쟁률</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
@@ -21515,6 +23914,16 @@
           <t>4.65 : 1</t>
         </is>
       </c>
+      <c r="Q37" s="8" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="R37" s="8" t="inlineStr">
+        <is>
+          <t>4.95 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
@@ -21597,9 +24006,19 @@
           <t>4.65 : 1</t>
         </is>
       </c>
+      <c r="Q38" s="8" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="R38" s="8" t="inlineStr">
+        <is>
+          <t>4.95 : 1</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="N1:O1"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="D1:E1"/>
@@ -21608,6 +24027,7 @@
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="F1:G1"/>
+    <mergeCell ref="R1:S1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -21619,13 +24039,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:S12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="39" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -21639,6 +24059,8 @@
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -21689,11 +24111,17 @@
         </is>
       </c>
       <c r="Q1" s="2" t="n"/>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>최종</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="D2" t="inlineStr">
         <is>
-          <t>대학의 마감일에는 10시, 14시, 15시, 최종해주시면 됩니다.</t>
+          <t>2027 수시모집 최종 경쟁률 마감 현황</t>
         </is>
       </c>
     </row>
@@ -21785,6 +24213,16 @@
           <t>경쟁률</t>
         </is>
       </c>
+      <c r="Q4" s="4" t="inlineStr">
+        <is>
+          <t>지원인원</t>
+        </is>
+      </c>
+      <c r="R4" s="4" t="inlineStr">
+        <is>
+          <t>경쟁률</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
@@ -21867,6 +24305,16 @@
           <t>23.0 : 1</t>
         </is>
       </c>
+      <c r="Q5" s="8" t="inlineStr">
+        <is>
+          <t>1,001</t>
+        </is>
+      </c>
+      <c r="R5" s="8" t="inlineStr">
+        <is>
+          <t>23.8 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -21949,6 +24397,16 @@
           <t>3.6 : 1</t>
         </is>
       </c>
+      <c r="Q6" s="8" t="inlineStr">
+        <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="R6" s="8" t="inlineStr">
+        <is>
+          <t>3.7 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -22031,6 +24489,16 @@
           <t>6.4 : 1</t>
         </is>
       </c>
+      <c r="Q7" s="8" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="R7" s="8" t="inlineStr">
+        <is>
+          <t>6.6 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -22113,6 +24581,16 @@
           <t>7.8 : 1</t>
         </is>
       </c>
+      <c r="Q8" s="8" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="R8" s="8" t="inlineStr">
+        <is>
+          <t>8.2 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -22195,6 +24673,16 @@
           <t>8.4 : 1</t>
         </is>
       </c>
+      <c r="Q9" s="8" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="R9" s="8" t="inlineStr">
+        <is>
+          <t>8.7 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -22277,6 +24765,16 @@
           <t>3.9 : 1</t>
         </is>
       </c>
+      <c r="Q10" s="8" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="R10" s="8" t="inlineStr">
+        <is>
+          <t>3.9 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -22359,6 +24857,16 @@
           <t>10.0 : 1</t>
         </is>
       </c>
+      <c r="Q11" s="8" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="R11" s="8" t="inlineStr">
+        <is>
+          <t>9.9 : 1</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -22441,9 +24949,19 @@
           <t>8.1 : 1</t>
         </is>
       </c>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>1,741</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>8.3 : 1</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="N1:O1"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="D1:E1"/>
@@ -22452,6 +24970,7 @@
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="F1:G1"/>
+    <mergeCell ref="R1:S1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/web/public/2027학년도_수시_교대경쟁률취합_정보분석3팀_최신.xlsx
+++ b/web/public/2027학년도_수시_교대경쟁률취합_정보분석3팀_최신.xlsx
@@ -507,7 +507,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:S15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -1641,7 +1641,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:S12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -2584,7 +2584,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:S7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -2971,7 +2971,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:S6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -3277,7 +3277,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:S29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -5359,7 +5359,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:S14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -6401,7 +6401,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:S10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -7075,7 +7075,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:S38"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -9815,7 +9815,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:S6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -10121,7 +10121,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:S7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -10508,7 +10508,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:S63"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -15123,7 +15123,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:S56"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -19204,7 +19204,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:S11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -20055,7 +20055,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:S7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -20442,7 +20442,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:S12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -21385,7 +21385,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:S38"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -24040,7 +24040,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:S12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>

--- a/web/public/2027학년도_수시_교대경쟁률취합_정보분석3팀_최신.xlsx
+++ b/web/public/2027학년도_수시_교대경쟁률취합_정보분석3팀_최신.xlsx
@@ -506,28 +506,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:R15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="11" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -536,57 +535,58 @@
           <t>전체 경쟁률 현황</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>09월07일20시</t>
         </is>
       </c>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>09월08일20시</t>
         </is>
       </c>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>09월09일20시</t>
         </is>
       </c>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>09월10일20시</t>
         </is>
       </c>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>09월11일10시</t>
         </is>
       </c>
-      <c r="M1" s="2" t="n"/>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="L1" s="2" t="n"/>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>09월11일14시</t>
         </is>
       </c>
-      <c r="O1" s="2" t="n"/>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="N1" s="2" t="n"/>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>09월11일15시</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="n"/>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="P1" s="2" t="n"/>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>최종</t>
         </is>
       </c>
-      <c r="S1" s="2" t="n"/>
+      <c r="R1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="D2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>2027 수시모집 최종 경쟁률 마감 현황</t>
         </is>
@@ -702,7 +702,7 @@
           <t>402</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>326</t>
         </is>
@@ -893,7 +893,7 @@
           <t>110</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>54</t>
         </is>
@@ -985,7 +985,7 @@
           <t>226</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>209</t>
         </is>
@@ -1077,7 +1077,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1169,7 +1169,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>21</t>
         </is>
@@ -1261,7 +1261,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -1353,7 +1353,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>21</t>
         </is>
@@ -1445,7 +1445,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -1537,7 +1537,7 @@
           <t>402</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>326</t>
         </is>
@@ -1620,15 +1620,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="I1:J1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1640,28 +1640,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:R12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1670,57 +1669,58 @@
           <t>전체 경쟁률 현황</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>09월07일20시</t>
         </is>
       </c>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>09월08일20시</t>
         </is>
       </c>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>09월09일20시</t>
         </is>
       </c>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>09월10일20시</t>
         </is>
       </c>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>09월11일10시</t>
         </is>
       </c>
-      <c r="M1" s="2" t="n"/>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="L1" s="2" t="n"/>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>09월11일14시</t>
         </is>
       </c>
-      <c r="O1" s="2" t="n"/>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="N1" s="2" t="n"/>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>09월11일15시</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="n"/>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="P1" s="2" t="n"/>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>최종</t>
         </is>
       </c>
-      <c r="S1" s="2" t="n"/>
+      <c r="R1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="D2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>2027 수시모집 최종 경쟁률 마감 현황</t>
         </is>
@@ -1836,7 +1836,7 @@
           <t>96</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>105</t>
         </is>
@@ -1928,7 +1928,7 @@
           <t>60</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>22</t>
         </is>
@@ -2020,7 +2020,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -2112,7 +2112,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -2204,7 +2204,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>21</t>
         </is>
@@ -2296,7 +2296,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -2388,7 +2388,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -2480,7 +2480,7 @@
           <t>184</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>166</t>
         </is>
@@ -2563,15 +2563,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="I1:J1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2583,28 +2583,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:R7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="10" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2613,57 +2612,58 @@
           <t>전체 경쟁률 현황</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>09월07일20시</t>
         </is>
       </c>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>09월08일20시</t>
         </is>
       </c>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>09월09일20시</t>
         </is>
       </c>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>09월10일20시</t>
         </is>
       </c>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>09월11일10시</t>
         </is>
       </c>
-      <c r="M1" s="2" t="n"/>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="L1" s="2" t="n"/>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>09월11일14시</t>
         </is>
       </c>
-      <c r="O1" s="2" t="n"/>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="N1" s="2" t="n"/>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>09월11일15시</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="n"/>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="P1" s="2" t="n"/>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>최종</t>
         </is>
       </c>
-      <c r="S1" s="2" t="n"/>
+      <c r="R1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="D2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>2027 수시모집 최종 경쟁률 마감 현황</t>
         </is>
@@ -2779,7 +2779,7 @@
           <t>77</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr"/>
+      <c r="C5" s="8" t="inlineStr"/>
       <c r="D5" s="8" t="inlineStr"/>
       <c r="E5" s="8" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
           <t>33</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr"/>
+      <c r="C6" s="8" t="inlineStr"/>
       <c r="D6" s="8" t="inlineStr"/>
       <c r="E6" s="8" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
           <t>110</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr"/>
+      <c r="C7" s="6" t="inlineStr"/>
       <c r="D7" s="6" t="inlineStr"/>
       <c r="E7" s="6" t="inlineStr">
         <is>
@@ -2950,15 +2950,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="I1:J1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2970,28 +2970,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:R6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3000,57 +2999,58 @@
           <t>전체 경쟁률 현황</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>09월07일20시</t>
         </is>
       </c>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>09월08일20시</t>
         </is>
       </c>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>09월09일20시</t>
         </is>
       </c>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>09월10일20시</t>
         </is>
       </c>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>09월11일10시</t>
         </is>
       </c>
-      <c r="M1" s="2" t="n"/>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="L1" s="2" t="n"/>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>09월11일14시</t>
         </is>
       </c>
-      <c r="O1" s="2" t="n"/>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="N1" s="2" t="n"/>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>09월11일15시</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="n"/>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="P1" s="2" t="n"/>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>최종</t>
         </is>
       </c>
-      <c r="S1" s="2" t="n"/>
+      <c r="R1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="D2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>2027 수시모집 최종 경쟁률 마감 현황</t>
         </is>
@@ -3173,7 +3173,7 @@
           <t>322</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>1,255</t>
         </is>
@@ -3256,15 +3256,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="I1:J1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3276,28 +3276,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:R29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3306,57 +3305,58 @@
           <t>전체 경쟁률 현황</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>09월07일20시</t>
         </is>
       </c>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>09월08일20시</t>
         </is>
       </c>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>09월09일20시</t>
         </is>
       </c>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>09월10일20시</t>
         </is>
       </c>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>09월11일10시</t>
         </is>
       </c>
-      <c r="M1" s="2" t="n"/>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="L1" s="2" t="n"/>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>09월11일14시</t>
         </is>
       </c>
-      <c r="O1" s="2" t="n"/>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="N1" s="2" t="n"/>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>09월11일15시</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="n"/>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="P1" s="2" t="n"/>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>최종</t>
         </is>
       </c>
-      <c r="S1" s="2" t="n"/>
+      <c r="R1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="D2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>2027 수시모집 최종 경쟁률 마감 현황</t>
         </is>
@@ -3472,7 +3472,7 @@
           <t>315</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>503</t>
         </is>
@@ -3663,7 +3663,7 @@
           <t>220</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>398</t>
         </is>
@@ -3755,7 +3755,7 @@
           <t>60</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>33</t>
         </is>
@@ -3847,7 +3847,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>44</t>
         </is>
@@ -3939,7 +3939,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>28</t>
         </is>
@@ -4031,7 +4031,7 @@
           <t>315</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>503</t>
         </is>
@@ -4222,7 +4222,7 @@
           <t>195</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>346</t>
         </is>
@@ -4314,7 +4314,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>52</t>
         </is>
@@ -4406,7 +4406,7 @@
           <t>220</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>398</t>
         </is>
@@ -4597,7 +4597,7 @@
           <t>60</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>33</t>
         </is>
@@ -4689,7 +4689,7 @@
           <t>60</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>33</t>
         </is>
@@ -4880,7 +4880,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>44</t>
         </is>
@@ -4972,7 +4972,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>44</t>
         </is>
@@ -5163,7 +5163,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
         <is>
           <t>28</t>
         </is>
@@ -5255,7 +5255,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C29" s="8" t="inlineStr">
         <is>
           <t>28</t>
         </is>
@@ -5338,15 +5338,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="I1:J1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5358,28 +5358,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:R14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5388,57 +5387,58 @@
           <t>전체 경쟁률 현황</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>09월07일20시</t>
         </is>
       </c>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>09월08일20시</t>
         </is>
       </c>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>09월09일20시</t>
         </is>
       </c>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>09월10일20시</t>
         </is>
       </c>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>09월11일10시</t>
         </is>
       </c>
-      <c r="M1" s="2" t="n"/>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="L1" s="2" t="n"/>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>09월11일14시</t>
         </is>
       </c>
-      <c r="O1" s="2" t="n"/>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="N1" s="2" t="n"/>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>09월11일15시</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="n"/>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="P1" s="2" t="n"/>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>최종</t>
         </is>
       </c>
-      <c r="S1" s="2" t="n"/>
+      <c r="R1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="D2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>2027 수시모집 최종 경쟁률 마감 현황</t>
         </is>
@@ -5554,7 +5554,7 @@
           <t>865</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>3,082</t>
         </is>
@@ -5745,7 +5745,7 @@
           <t>270</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>1,217</t>
         </is>
@@ -5837,7 +5837,7 @@
           <t>85</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>228</t>
         </is>
@@ -5929,7 +5929,7 @@
           <t>380</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>1,333</t>
         </is>
@@ -6021,7 +6021,7 @@
           <t>60</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>155</t>
         </is>
@@ -6113,7 +6113,7 @@
           <t>30</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>104</t>
         </is>
@@ -6205,7 +6205,7 @@
           <t>40</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>45</t>
         </is>
@@ -6297,7 +6297,7 @@
           <t>865</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>3,082</t>
         </is>
@@ -6380,15 +6380,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="I1:J1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6400,28 +6400,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:R10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6430,57 +6429,58 @@
           <t>전체 경쟁률 현황</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>09월07일20시</t>
         </is>
       </c>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>09월08일20시</t>
         </is>
       </c>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>09월09일20시</t>
         </is>
       </c>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>09월10일20시</t>
         </is>
       </c>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>09월11일10시</t>
         </is>
       </c>
-      <c r="M1" s="2" t="n"/>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="L1" s="2" t="n"/>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>09월11일14시</t>
         </is>
       </c>
-      <c r="O1" s="2" t="n"/>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="N1" s="2" t="n"/>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>09월11일15시</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="n"/>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="P1" s="2" t="n"/>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>최종</t>
         </is>
       </c>
-      <c r="S1" s="2" t="n"/>
+      <c r="R1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="D2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>2027 수시모집 최종 경쟁률 마감 현황</t>
         </is>
@@ -6596,7 +6596,7 @@
           <t>100</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>290</t>
         </is>
@@ -6787,7 +6787,7 @@
           <t>90</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>265</t>
         </is>
@@ -6879,7 +6879,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>25</t>
         </is>
@@ -6971,7 +6971,7 @@
           <t>100</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>290</t>
         </is>
@@ -7054,15 +7054,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="I1:J1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7074,28 +7074,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S38"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:R38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7104,57 +7103,58 @@
           <t>전체 경쟁률 현황</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>09월07일20시</t>
         </is>
       </c>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>09월08일20시</t>
         </is>
       </c>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>09월09일20시</t>
         </is>
       </c>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>09월10일20시</t>
         </is>
       </c>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>09월11일10시</t>
         </is>
       </c>
-      <c r="M1" s="2" t="n"/>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="L1" s="2" t="n"/>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>09월11일14시</t>
         </is>
       </c>
-      <c r="O1" s="2" t="n"/>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="N1" s="2" t="n"/>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>09월11일15시</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="n"/>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="P1" s="2" t="n"/>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>최종</t>
         </is>
       </c>
-      <c r="S1" s="2" t="n"/>
+      <c r="R1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="D2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>2027 수시모집 최종 경쟁률 마감 현황</t>
         </is>
@@ -7270,7 +7270,7 @@
           <t>370</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>848</t>
         </is>
@@ -7461,7 +7461,7 @@
           <t>220</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>591</t>
         </is>
@@ -7553,7 +7553,7 @@
           <t>70</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>78</t>
         </is>
@@ -7645,7 +7645,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -7737,7 +7737,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>28</t>
         </is>
@@ -7829,7 +7829,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -7921,7 +7921,7 @@
           <t>40</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>126</t>
         </is>
@@ -8013,7 +8013,7 @@
           <t>370</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>848</t>
         </is>
@@ -8204,7 +8204,7 @@
           <t>220</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>591</t>
         </is>
@@ -8296,7 +8296,7 @@
           <t>220</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>591</t>
         </is>
@@ -8487,7 +8487,7 @@
           <t>70</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>78</t>
         </is>
@@ -8579,7 +8579,7 @@
           <t>70</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>78</t>
         </is>
@@ -8770,7 +8770,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -8862,7 +8862,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -9053,7 +9053,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C29" s="8" t="inlineStr">
         <is>
           <t>28</t>
         </is>
@@ -9145,7 +9145,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C30" s="8" t="inlineStr">
         <is>
           <t>28</t>
         </is>
@@ -9336,7 +9336,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C33" s="8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -9428,7 +9428,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C34" s="8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -9619,7 +9619,7 @@
           <t>40</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr">
+      <c r="C37" s="8" t="inlineStr">
         <is>
           <t>126</t>
         </is>
@@ -9711,7 +9711,7 @@
           <t>40</t>
         </is>
       </c>
-      <c r="C38" s="7" t="inlineStr">
+      <c r="C38" s="8" t="inlineStr">
         <is>
           <t>126</t>
         </is>
@@ -9794,15 +9794,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="I1:J1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9814,28 +9814,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:R6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9844,57 +9843,58 @@
           <t>전체 경쟁률 현황</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>09월07일20시</t>
         </is>
       </c>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>09월08일20시</t>
         </is>
       </c>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>09월09일20시</t>
         </is>
       </c>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>09월10일20시</t>
         </is>
       </c>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>09월11일10시</t>
         </is>
       </c>
-      <c r="M1" s="2" t="n"/>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="L1" s="2" t="n"/>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>09월11일14시</t>
         </is>
       </c>
-      <c r="O1" s="2" t="n"/>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="N1" s="2" t="n"/>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>09월11일15시</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="n"/>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="P1" s="2" t="n"/>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>최종</t>
         </is>
       </c>
-      <c r="S1" s="2" t="n"/>
+      <c r="R1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="D2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>2027 수시모집 최종 경쟁률 마감 현황</t>
         </is>
@@ -10017,7 +10017,7 @@
           <t>565</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>1,736</t>
         </is>
@@ -10100,15 +10100,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="I1:J1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10120,28 +10120,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:R7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="10" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10150,57 +10149,58 @@
           <t>전체 경쟁률 현황</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>09월07일20시</t>
         </is>
       </c>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>09월08일20시</t>
         </is>
       </c>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>09월09일20시</t>
         </is>
       </c>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>09월10일20시</t>
         </is>
       </c>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>09월11일10시</t>
         </is>
       </c>
-      <c r="M1" s="2" t="n"/>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="L1" s="2" t="n"/>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>09월11일14시</t>
         </is>
       </c>
-      <c r="O1" s="2" t="n"/>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="N1" s="2" t="n"/>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>09월11일15시</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="n"/>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="P1" s="2" t="n"/>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>최종</t>
         </is>
       </c>
-      <c r="S1" s="2" t="n"/>
+      <c r="R1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="D2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>2027 수시모집 최종 경쟁률 마감 현황</t>
         </is>
@@ -10316,7 +10316,7 @@
           <t>140</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr"/>
+      <c r="C5" s="8" t="inlineStr"/>
       <c r="D5" s="8" t="inlineStr"/>
       <c r="E5" s="8" t="inlineStr">
         <is>
@@ -10376,7 +10376,7 @@
           <t>60</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr"/>
+      <c r="C6" s="8" t="inlineStr"/>
       <c r="D6" s="8" t="inlineStr"/>
       <c r="E6" s="8" t="inlineStr">
         <is>
@@ -10436,7 +10436,7 @@
           <t>200</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr"/>
+      <c r="C7" s="6" t="inlineStr"/>
       <c r="D7" s="6" t="inlineStr"/>
       <c r="E7" s="6" t="inlineStr">
         <is>
@@ -10487,15 +10487,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="I1:J1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10507,28 +10507,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S63"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:R63"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10537,57 +10536,58 @@
           <t>전체 경쟁률 현황</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>09월07일20시</t>
         </is>
       </c>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>09월08일20시</t>
         </is>
       </c>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>09월09일20시</t>
         </is>
       </c>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>09월10일20시</t>
         </is>
       </c>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>09월11일10시</t>
         </is>
       </c>
-      <c r="M1" s="2" t="n"/>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="L1" s="2" t="n"/>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>09월11일14시</t>
         </is>
       </c>
-      <c r="O1" s="2" t="n"/>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="N1" s="2" t="n"/>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>09월11일15시</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="n"/>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="P1" s="2" t="n"/>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>최종</t>
         </is>
       </c>
-      <c r="S1" s="2" t="n"/>
+      <c r="R1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="D2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>2027 수시모집 최종 경쟁률 마감 현황</t>
         </is>
@@ -10703,7 +10703,7 @@
           <t>272</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>211</t>
         </is>
@@ -10894,7 +10894,7 @@
           <t>50</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -10986,7 +10986,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -11078,7 +11078,7 @@
           <t>53</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>79</t>
         </is>
@@ -11170,7 +11170,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>19</t>
         </is>
@@ -11262,7 +11262,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>13</t>
         </is>
@@ -11354,7 +11354,7 @@
           <t>60</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>35</t>
         </is>
@@ -11446,7 +11446,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -11538,7 +11538,7 @@
           <t>50</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -11630,7 +11630,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -11722,7 +11722,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -11814,7 +11814,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>21</t>
         </is>
@@ -11906,7 +11906,7 @@
           <t>272</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>211</t>
         </is>
@@ -12097,7 +12097,7 @@
           <t>50</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -12189,7 +12189,7 @@
           <t>50</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -12380,7 +12380,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -12472,7 +12472,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C27" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -12663,7 +12663,7 @@
           <t>53</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C30" s="8" t="inlineStr">
         <is>
           <t>79</t>
         </is>
@@ -12755,7 +12755,7 @@
           <t>53</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C31" s="8" t="inlineStr">
         <is>
           <t>79</t>
         </is>
@@ -12946,7 +12946,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C34" s="8" t="inlineStr">
         <is>
           <t>19</t>
         </is>
@@ -13038,7 +13038,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
+      <c r="C35" s="8" t="inlineStr">
         <is>
           <t>19</t>
         </is>
@@ -13229,7 +13229,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C38" s="7" t="inlineStr">
+      <c r="C38" s="8" t="inlineStr">
         <is>
           <t>13</t>
         </is>
@@ -13321,7 +13321,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C39" s="7" t="inlineStr">
+      <c r="C39" s="8" t="inlineStr">
         <is>
           <t>13</t>
         </is>
@@ -13512,7 +13512,7 @@
           <t>60</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C42" s="8" t="inlineStr">
         <is>
           <t>35</t>
         </is>
@@ -13604,7 +13604,7 @@
           <t>60</t>
         </is>
       </c>
-      <c r="C43" s="7" t="inlineStr">
+      <c r="C43" s="8" t="inlineStr">
         <is>
           <t>35</t>
         </is>
@@ -13795,7 +13795,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C46" s="7" t="inlineStr">
+      <c r="C46" s="8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -13887,7 +13887,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C47" s="7" t="inlineStr">
+      <c r="C47" s="8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -14078,7 +14078,7 @@
           <t>50</t>
         </is>
       </c>
-      <c r="C50" s="7" t="inlineStr">
+      <c r="C50" s="8" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -14170,7 +14170,7 @@
           <t>50</t>
         </is>
       </c>
-      <c r="C51" s="7" t="inlineStr">
+      <c r="C51" s="8" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -14361,7 +14361,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C54" s="7" t="inlineStr">
+      <c r="C54" s="8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -14453,7 +14453,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C55" s="7" t="inlineStr">
+      <c r="C55" s="8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -14644,7 +14644,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C58" s="7" t="inlineStr">
+      <c r="C58" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -14736,7 +14736,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C59" s="7" t="inlineStr">
+      <c r="C59" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -14927,7 +14927,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C62" s="7" t="inlineStr">
+      <c r="C62" s="8" t="inlineStr">
         <is>
           <t>21</t>
         </is>
@@ -15019,7 +15019,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C63" s="7" t="inlineStr">
+      <c r="C63" s="8" t="inlineStr">
         <is>
           <t>21</t>
         </is>
@@ -15102,15 +15102,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="I1:J1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15123,21 +15123,21 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:S56"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
@@ -15152,57 +15152,58 @@
           <t>전체 경쟁률 현황</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>09월07일20시</t>
         </is>
       </c>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>09월08일20시</t>
         </is>
       </c>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>09월09일20시</t>
         </is>
       </c>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>09월10일20시</t>
         </is>
       </c>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>09월11일10시</t>
         </is>
       </c>
-      <c r="M1" s="2" t="n"/>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="L1" s="2" t="n"/>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>09월11일14시</t>
         </is>
       </c>
-      <c r="O1" s="2" t="n"/>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="N1" s="2" t="n"/>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>09월11일15시</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="n"/>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="P1" s="2" t="n"/>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>최종</t>
         </is>
       </c>
-      <c r="S1" s="2" t="n"/>
+      <c r="R1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="D2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>2027 수시모집 최종 경쟁률 마감 현황</t>
         </is>
@@ -15318,7 +15319,7 @@
           <t>310</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>122</t>
         </is>
@@ -15509,7 +15510,7 @@
           <t>50</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>41</t>
         </is>
@@ -15601,7 +15602,7 @@
           <t>90</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>26</t>
         </is>
@@ -15693,7 +15694,7 @@
           <t>127</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>36</t>
         </is>
@@ -15785,7 +15786,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -15877,7 +15878,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -15969,7 +15970,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -16061,7 +16062,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -16153,7 +16154,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -16245,7 +16246,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -16337,7 +16338,7 @@
           <t>310</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>122</t>
         </is>
@@ -16533,7 +16534,7 @@
           <t>초등교육과</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>50</t>
         </is>
@@ -16630,7 +16631,7 @@
           <t>초등교육과</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr"/>
+      <c r="C21" s="8" t="inlineStr"/>
       <c r="D21" s="8" t="inlineStr">
         <is>
           <t>24</t>
@@ -16687,7 +16688,7 @@
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr"/>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>50</t>
         </is>
@@ -16888,7 +16889,7 @@
           <t>초등교육과</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>90</t>
         </is>
@@ -16985,7 +16986,7 @@
           <t>초등교육과</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr"/>
+      <c r="C26" s="8" t="inlineStr"/>
       <c r="D26" s="8" t="inlineStr">
         <is>
           <t>19</t>
@@ -17042,7 +17043,7 @@
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr"/>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C27" s="8" t="inlineStr">
         <is>
           <t>90</t>
         </is>
@@ -17243,7 +17244,7 @@
           <t>초등교육과</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C30" s="8" t="inlineStr">
         <is>
           <t>127</t>
         </is>
@@ -17340,7 +17341,7 @@
           <t>초등교육과</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr"/>
+      <c r="C31" s="8" t="inlineStr"/>
       <c r="D31" s="8" t="inlineStr">
         <is>
           <t>19</t>
@@ -17397,7 +17398,7 @@
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr"/>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C32" s="8" t="inlineStr">
         <is>
           <t>127</t>
         </is>
@@ -17593,7 +17594,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
+      <c r="C35" s="8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -17685,7 +17686,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
+      <c r="C36" s="8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -17876,7 +17877,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="C39" s="7" t="inlineStr">
+      <c r="C39" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -17968,7 +17969,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="C40" s="7" t="inlineStr">
+      <c r="C40" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -18159,7 +18160,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="C43" s="7" t="inlineStr">
+      <c r="C43" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -18251,7 +18252,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="C44" s="7" t="inlineStr">
+      <c r="C44" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -18442,7 +18443,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="C47" s="7" t="inlineStr">
+      <c r="C47" s="8" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -18534,7 +18535,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="C48" s="7" t="inlineStr">
+      <c r="C48" s="8" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -18725,7 +18726,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C51" s="7" t="inlineStr">
+      <c r="C51" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -18817,7 +18818,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C52" s="7" t="inlineStr">
+      <c r="C52" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -19008,7 +19009,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C55" s="7" t="inlineStr">
+      <c r="C55" s="8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -19100,7 +19101,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C56" s="7" t="inlineStr">
+      <c r="C56" s="8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -19183,15 +19184,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="I1:J1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19203,28 +19204,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:R11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="11" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19233,57 +19233,58 @@
           <t>전체 경쟁률 현황</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>09월07일20시</t>
         </is>
       </c>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>09월08일20시</t>
         </is>
       </c>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>09월09일20시</t>
         </is>
       </c>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>09월10일20시</t>
         </is>
       </c>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>09월11일10시</t>
         </is>
       </c>
-      <c r="M1" s="2" t="n"/>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="L1" s="2" t="n"/>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>09월11일14시</t>
         </is>
       </c>
-      <c r="O1" s="2" t="n"/>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="N1" s="2" t="n"/>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>09월11일15시</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="n"/>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="P1" s="2" t="n"/>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>최종</t>
         </is>
       </c>
-      <c r="S1" s="2" t="n"/>
+      <c r="R1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="D2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>2027 수시모집 최종 경쟁률 마감 현황</t>
         </is>
@@ -19399,7 +19400,7 @@
           <t>65</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>38</t>
         </is>
@@ -19491,7 +19492,7 @@
           <t>125</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>64</t>
         </is>
@@ -19583,7 +19584,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -19675,7 +19676,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -19767,7 +19768,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -19859,7 +19860,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -19951,7 +19952,7 @@
           <t>222</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>120</t>
         </is>
@@ -20034,15 +20035,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="I1:J1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -20054,28 +20055,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:R7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="10" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -20084,57 +20084,58 @@
           <t>전체 경쟁률 현황</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>09월07일20시</t>
         </is>
       </c>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>09월08일20시</t>
         </is>
       </c>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>09월09일20시</t>
         </is>
       </c>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>09월10일20시</t>
         </is>
       </c>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>09월11일10시</t>
         </is>
       </c>
-      <c r="M1" s="2" t="n"/>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="L1" s="2" t="n"/>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>09월11일14시</t>
         </is>
       </c>
-      <c r="O1" s="2" t="n"/>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="N1" s="2" t="n"/>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>09월11일15시</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="n"/>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="P1" s="2" t="n"/>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>최종</t>
         </is>
       </c>
-      <c r="S1" s="2" t="n"/>
+      <c r="R1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="D2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>2027 수시모집 최종 경쟁률 마감 현황</t>
         </is>
@@ -20250,7 +20251,7 @@
           <t>133</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr"/>
+      <c r="C5" s="8" t="inlineStr"/>
       <c r="D5" s="8" t="inlineStr"/>
       <c r="E5" s="8" t="inlineStr">
         <is>
@@ -20310,7 +20311,7 @@
           <t>57</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr"/>
+      <c r="C6" s="8" t="inlineStr"/>
       <c r="D6" s="8" t="inlineStr"/>
       <c r="E6" s="8" t="inlineStr">
         <is>
@@ -20370,7 +20371,7 @@
           <t>190</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr"/>
+      <c r="C7" s="6" t="inlineStr"/>
       <c r="D7" s="6" t="inlineStr"/>
       <c r="E7" s="6" t="inlineStr">
         <is>
@@ -20421,15 +20422,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="I1:J1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -20441,28 +20442,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:R12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -20471,57 +20471,58 @@
           <t>전체 경쟁률 현황</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>09월07일20시</t>
         </is>
       </c>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>09월08일20시</t>
         </is>
       </c>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>09월09일20시</t>
         </is>
       </c>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>09월10일20시</t>
         </is>
       </c>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>09월11일10시</t>
         </is>
       </c>
-      <c r="M1" s="2" t="n"/>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="L1" s="2" t="n"/>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>09월11일14시</t>
         </is>
       </c>
-      <c r="O1" s="2" t="n"/>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="N1" s="2" t="n"/>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>09월11일15시</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="n"/>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="P1" s="2" t="n"/>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>최종</t>
         </is>
       </c>
-      <c r="S1" s="2" t="n"/>
+      <c r="R1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="D2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>2027 수시모집 최종 경쟁률 마감 현황</t>
         </is>
@@ -20637,7 +20638,7 @@
           <t>48</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>65</t>
         </is>
@@ -20729,7 +20730,7 @@
           <t>114</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>35</t>
         </is>
@@ -20821,7 +20822,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -20913,7 +20914,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -21005,7 +21006,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -21097,7 +21098,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -21189,7 +21190,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -21281,7 +21282,7 @@
           <t>195</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>127</t>
         </is>
@@ -21364,15 +21365,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="I1:J1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -21384,28 +21385,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S38"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:R38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -21414,57 +21414,58 @@
           <t>전체 경쟁률 현황</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>09월07일20시</t>
         </is>
       </c>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>09월08일20시</t>
         </is>
       </c>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>09월09일20시</t>
         </is>
       </c>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>09월10일20시</t>
         </is>
       </c>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>09월11일10시</t>
         </is>
       </c>
-      <c r="M1" s="2" t="n"/>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="L1" s="2" t="n"/>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>09월11일14시</t>
         </is>
       </c>
-      <c r="O1" s="2" t="n"/>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="N1" s="2" t="n"/>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>09월11일15시</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="n"/>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="P1" s="2" t="n"/>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>최종</t>
         </is>
       </c>
-      <c r="S1" s="2" t="n"/>
+      <c r="R1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="D2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>2027 수시모집 최종 경쟁률 마감 현황</t>
         </is>
@@ -21580,7 +21581,7 @@
           <t>50</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>44</t>
         </is>
@@ -21672,7 +21673,7 @@
           <t>123</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>72</t>
         </is>
@@ -21764,7 +21765,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -21856,7 +21857,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -21948,7 +21949,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>30</t>
         </is>
@@ -22040,7 +22041,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -22132,7 +22133,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -22224,7 +22225,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>24</t>
         </is>
@@ -22316,7 +22317,7 @@
           <t>228</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>184</t>
         </is>
@@ -22507,7 +22508,7 @@
           <t>50</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>44</t>
         </is>
@@ -22698,7 +22699,7 @@
           <t>123</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>72</t>
         </is>
@@ -22889,7 +22890,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -23080,7 +23081,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -23271,7 +23272,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
         <is>
           <t>30</t>
         </is>
@@ -23462,7 +23463,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C31" s="8" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -23653,7 +23654,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C34" s="8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -23844,7 +23845,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr">
+      <c r="C37" s="8" t="inlineStr">
         <is>
           <t>24</t>
         </is>
@@ -23936,7 +23937,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="C38" s="7" t="inlineStr">
+      <c r="C38" s="8" t="inlineStr">
         <is>
           <t>24</t>
         </is>
@@ -24019,15 +24020,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="I1:J1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -24039,28 +24040,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:R12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="11" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -24069,57 +24069,58 @@
           <t>전체 경쟁률 현황</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>09월07일20시</t>
         </is>
       </c>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>09월08일20시</t>
         </is>
       </c>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>09월09일20시</t>
         </is>
       </c>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>09월10일20시</t>
         </is>
       </c>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>09월11일10시</t>
         </is>
       </c>
-      <c r="M1" s="2" t="n"/>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="L1" s="2" t="n"/>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>09월11일14시</t>
         </is>
       </c>
-      <c r="O1" s="2" t="n"/>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="N1" s="2" t="n"/>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>09월11일15시</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="n"/>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="P1" s="2" t="n"/>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>최종</t>
         </is>
       </c>
-      <c r="S1" s="2" t="n"/>
+      <c r="R1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="D2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>2027 수시모집 최종 경쟁률 마감 현황</t>
         </is>
@@ -24235,7 +24236,7 @@
           <t>42</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>112</t>
         </is>
@@ -24327,7 +24328,7 @@
           <t>132</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>54</t>
         </is>
@@ -24419,7 +24420,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -24511,7 +24512,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -24603,7 +24604,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -24695,7 +24696,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -24787,7 +24788,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>13</t>
         </is>
@@ -24879,7 +24880,7 @@
           <t>209</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>212</t>
         </is>
@@ -24962,15 +24963,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="I1:J1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
